--- a/Other/RoStatProcessing.xlsx
+++ b/Other/RoStatProcessing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProjectsSSD\RagnarokRebuildTcp\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B954FCCB-58D8-4CD1-87E2-1FC3CF582267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0418A210-368A-4AD8-88DA-462608D61300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="497" yWindow="2606" windowWidth="31080" windowHeight="14828" firstSheet="3" activeTab="7" xr2:uid="{1C41742B-2950-4FF8-AA39-6557869B44EA}"/>
+    <workbookView xWindow="4946" yWindow="3463" windowWidth="23725" windowHeight="12643" xr2:uid="{1C41742B-2950-4FF8-AA39-6557869B44EA}"/>
   </bookViews>
   <sheets>
     <sheet name="StatDef" sheetId="3" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3328" uniqueCount="1236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3337" uniqueCount="1239">
   <si>
     <t>Id</t>
   </si>
@@ -3761,6 +3761,15 @@
   </si>
   <si>
     <t>SecondJob</t>
+  </si>
+  <si>
+    <t>FUBUKI</t>
+  </si>
+  <si>
+    <t>Fubuki</t>
+  </si>
+  <si>
+    <t>fubuki.asset</t>
   </si>
 </sst>
 </file>
@@ -4211,7 +4220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811A97A5-94A7-4FFA-A162-65D076B52481}">
-  <dimension ref="A1:AK325"/>
+  <dimension ref="A1:AK326"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.07421875" bestFit="1" customWidth="1"/>
@@ -39346,6 +39355,113 @@
         <v>1</v>
       </c>
     </row>
+    <row r="326" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A326">
+        <v>6022</v>
+      </c>
+      <c r="B326" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C326" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D326">
+        <v>62</v>
+      </c>
+      <c r="E326">
+        <v>60</v>
+      </c>
+      <c r="F326">
+        <v>100</v>
+      </c>
+      <c r="G326">
+        <v>10</v>
+      </c>
+      <c r="H326">
+        <v>30</v>
+      </c>
+      <c r="I326">
+        <v>130</v>
+      </c>
+      <c r="J326">
+        <v>100</v>
+      </c>
+      <c r="K326">
+        <v>100</v>
+      </c>
+      <c r="L326">
+        <v>80</v>
+      </c>
+      <c r="M326">
+        <v>15</v>
+      </c>
+      <c r="N326">
+        <v>9</v>
+      </c>
+      <c r="O326">
+        <v>120</v>
+      </c>
+      <c r="P326">
+        <v>30</v>
+      </c>
+      <c r="Q326">
+        <v>90</v>
+      </c>
+      <c r="R326">
+        <v>90</v>
+      </c>
+      <c r="S326">
+        <v>10</v>
+      </c>
+      <c r="T326">
+        <v>12</v>
+      </c>
+      <c r="U326" t="s">
+        <v>38</v>
+      </c>
+      <c r="V326" t="s">
+        <v>160</v>
+      </c>
+      <c r="W326" t="s">
+        <v>532</v>
+      </c>
+      <c r="X326">
+        <v>1000</v>
+      </c>
+      <c r="Y326">
+        <v>750</v>
+      </c>
+      <c r="Z326">
+        <v>1000</v>
+      </c>
+      <c r="AA326">
+        <v>160</v>
+      </c>
+      <c r="AB326" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC326" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AD326" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF326">
+        <v>972</v>
+      </c>
+      <c r="AG326" t="s">
+        <v>1238</v>
+      </c>
+      <c r="AH326">
+        <v>0</v>
+      </c>
+      <c r="AI326">
+        <v>0.5</v>
+      </c>
+      <c r="AJ326">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AJ180">
     <sortCondition ref="D3:D180"/>
@@ -65604,7 +65720,7 @@
         <v>1060506</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E70" si="2">(C68/C67-1)*(1-(A67/500))+1</f>
+        <f t="shared" ref="E67:E69" si="2">(C68/C67-1)*(1-(A67/500))+1</f>
         <v>1.0718704844668487</v>
       </c>
       <c r="F67">

--- a/Other/RoStatProcessing.xlsx
+++ b/Other/RoStatProcessing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProjectsSSD\RagnarokRebuildTcp\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0418A210-368A-4AD8-88DA-462608D61300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1BC145-16DC-4AFC-B66F-F14CB919AEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4946" yWindow="3463" windowWidth="23725" windowHeight="12643" xr2:uid="{1C41742B-2950-4FF8-AA39-6557869B44EA}"/>
+    <workbookView xWindow="5486" yWindow="1586" windowWidth="24034" windowHeight="14691" xr2:uid="{1C41742B-2950-4FF8-AA39-6557869B44EA}"/>
   </bookViews>
   <sheets>
     <sheet name="StatDef" sheetId="3" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3337" uniqueCount="1239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="1276">
   <si>
     <t>Id</t>
   </si>
@@ -2614,9 +2614,6 @@
     <t>DELETER</t>
   </si>
   <si>
-    <t>Deleter</t>
-  </si>
-  <si>
     <t>deleter.spr</t>
   </si>
   <si>
@@ -3770,6 +3767,120 @@
   </si>
   <si>
     <t>fubuki.asset</t>
+  </si>
+  <si>
+    <t>NIGHTMARE_TERROR</t>
+  </si>
+  <si>
+    <t>nightmare_terror.spr</t>
+  </si>
+  <si>
+    <t>Nightmare Terror</t>
+  </si>
+  <si>
+    <t>DARK_PRIEST</t>
+  </si>
+  <si>
+    <t>dark_priest.spr</t>
+  </si>
+  <si>
+    <t>Dark Priest</t>
+  </si>
+  <si>
+    <t>Strong,Undead</t>
+  </si>
+  <si>
+    <t>MINI_DEMON</t>
+  </si>
+  <si>
+    <t>mini_demon.spr</t>
+  </si>
+  <si>
+    <t>Mini Demon</t>
+  </si>
+  <si>
+    <t>ZOMBIE_MASTER</t>
+  </si>
+  <si>
+    <t>zombie_master.spr</t>
+  </si>
+  <si>
+    <t>Zombie Master</t>
+  </si>
+  <si>
+    <t>BLAZZER</t>
+  </si>
+  <si>
+    <t>blazzer.spr</t>
+  </si>
+  <si>
+    <t>Blazer</t>
+  </si>
+  <si>
+    <t>EXPLOSION</t>
+  </si>
+  <si>
+    <t>explosion.spr</t>
+  </si>
+  <si>
+    <t>Explosion</t>
+  </si>
+  <si>
+    <t>GRIZZLY</t>
+  </si>
+  <si>
+    <t>grizzly.spr</t>
+  </si>
+  <si>
+    <t>Grizzly</t>
+  </si>
+  <si>
+    <t>KAHO</t>
+  </si>
+  <si>
+    <t>kaho.spr</t>
+  </si>
+  <si>
+    <t>Kaho</t>
+  </si>
+  <si>
+    <t>LAVA_GOLEM</t>
+  </si>
+  <si>
+    <t>lava_golem.spr</t>
+  </si>
+  <si>
+    <t>Lava Golem</t>
+  </si>
+  <si>
+    <t>Sky Deleter</t>
+  </si>
+  <si>
+    <t>Earth Deleter</t>
+  </si>
+  <si>
+    <t>Elite,Golem</t>
+  </si>
+  <si>
+    <t>Dragon,Buff</t>
+  </si>
+  <si>
+    <t>DIABOLIC</t>
+  </si>
+  <si>
+    <t>diabolic.spr</t>
+  </si>
+  <si>
+    <t>Diabolic</t>
+  </si>
+  <si>
+    <t>GIG</t>
+  </si>
+  <si>
+    <t>gig.spr</t>
+  </si>
+  <si>
+    <t>Gig</t>
   </si>
 </sst>
 </file>
@@ -3875,10 +3986,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5AE4419D-5DB5-4D1B-9713-9E17C7E1903B}" name="Table1" displayName="Table1" ref="A1:AK414" totalsRowShown="0">
-  <autoFilter ref="A1:AK414" xr:uid="{5AE4419D-5DB5-4D1B-9713-9E17C7E1903B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AK318">
-    <sortCondition ref="A1:A414"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5AE4419D-5DB5-4D1B-9713-9E17C7E1903B}" name="Table1" displayName="Table1" ref="A1:AK425" totalsRowShown="0">
+  <autoFilter ref="A1:AK425" xr:uid="{5AE4419D-5DB5-4D1B-9713-9E17C7E1903B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AK331">
+    <sortCondition ref="A1:A425"/>
   </sortState>
   <tableColumns count="37">
     <tableColumn id="1" xr3:uid="{B859DFBF-EB68-4198-9FF0-FEBC6A5D6D92}" name="Id"/>
@@ -4220,7 +4331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811A97A5-94A7-4FFA-A162-65D076B52481}">
-  <dimension ref="A1:AK326"/>
+  <dimension ref="A1:AK337"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.07421875" bestFit="1" customWidth="1"/>
@@ -4351,7 +4462,7 @@
         <v>29</v>
       </c>
       <c r="AE1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="AF1" t="s">
         <v>30</v>
@@ -4377,10 +4488,10 @@
         <v>3999</v>
       </c>
       <c r="B2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C2" t="s">
         <v>1109</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1110</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -4568,7 +4679,7 @@
         <v>39</v>
       </c>
       <c r="AD3" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AF3">
         <v>288</v>
@@ -4999,7 +5110,7 @@
         <v>42</v>
       </c>
       <c r="AE7" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF7">
         <v>432</v>
@@ -5213,7 +5324,7 @@
         <v>39</v>
       </c>
       <c r="AD9" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AF9">
         <v>288</v>
@@ -5320,7 +5431,7 @@
         <v>48</v>
       </c>
       <c r="AD10" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AF10">
         <v>480</v>
@@ -5424,7 +5535,7 @@
         <v>41</v>
       </c>
       <c r="AC11" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="AD11" t="s">
         <v>59</v>
@@ -5537,7 +5648,7 @@
         <v>74</v>
       </c>
       <c r="AE12" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF12">
         <v>576</v>
@@ -5754,7 +5865,7 @@
         <v>59</v>
       </c>
       <c r="AE14" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -5861,7 +5972,7 @@
         <v>39</v>
       </c>
       <c r="AD15" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AF15">
         <v>288</v>
@@ -6078,7 +6189,7 @@
         <v>99</v>
       </c>
       <c r="AE17" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF17">
         <v>360</v>
@@ -6185,7 +6296,7 @@
         <v>41</v>
       </c>
       <c r="AD18" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF18">
         <v>252</v>
@@ -6292,7 +6403,7 @@
         <v>106</v>
       </c>
       <c r="AD19" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF19">
         <v>576</v>
@@ -6613,7 +6724,7 @@
         <v>120</v>
       </c>
       <c r="AD22" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF22">
         <v>264</v>
@@ -6720,7 +6831,7 @@
         <v>275</v>
       </c>
       <c r="AD23" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AF23">
         <v>360</v>
@@ -6827,7 +6938,7 @@
         <v>275</v>
       </c>
       <c r="AD24" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF24">
         <v>432</v>
@@ -6931,10 +7042,10 @@
         <v>41</v>
       </c>
       <c r="AC25" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="AD25" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF25">
         <v>360</v>
@@ -7472,7 +7583,7 @@
         <v>74</v>
       </c>
       <c r="AE30" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF30">
         <v>360</v>
@@ -7796,7 +7907,7 @@
         <v>59</v>
       </c>
       <c r="AE33" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -7903,10 +8014,10 @@
         <v>41</v>
       </c>
       <c r="AD34" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE34" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AF34">
         <v>384</v>
@@ -8013,10 +8124,10 @@
         <v>41</v>
       </c>
       <c r="AD35" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AE35" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AF35">
         <v>384</v>
@@ -8123,10 +8234,10 @@
         <v>41</v>
       </c>
       <c r="AD36" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AE36" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AF36">
         <v>384</v>
@@ -8233,10 +8344,10 @@
         <v>41</v>
       </c>
       <c r="AD37" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AE37" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AF37">
         <v>384</v>
@@ -8343,10 +8454,10 @@
         <v>41</v>
       </c>
       <c r="AD38" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AE38" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AF38">
         <v>384</v>
@@ -8456,7 +8567,7 @@
         <v>99</v>
       </c>
       <c r="AE39" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AF39">
         <v>528</v>
@@ -8563,10 +8674,10 @@
         <v>192</v>
       </c>
       <c r="AD40" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE40" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="AF40">
         <v>324</v>
@@ -8673,10 +8784,10 @@
         <v>41</v>
       </c>
       <c r="AD41" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AE41" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="AF41">
         <v>324</v>
@@ -8786,7 +8897,7 @@
         <v>99</v>
       </c>
       <c r="AE42" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="AF42">
         <v>1008</v>
@@ -8893,10 +9004,10 @@
         <v>192</v>
       </c>
       <c r="AD43" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE43" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AF43">
         <v>603</v>
@@ -9110,7 +9221,7 @@
         <v>275</v>
       </c>
       <c r="AD45" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF45">
         <v>192</v>
@@ -9327,7 +9438,7 @@
         <v>42</v>
       </c>
       <c r="AE47" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AF47">
         <v>528</v>
@@ -9648,7 +9759,7 @@
         <v>39</v>
       </c>
       <c r="AD50" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AF50">
         <v>288</v>
@@ -9755,10 +9866,10 @@
         <v>221</v>
       </c>
       <c r="AD51" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE51" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF51">
         <v>336</v>
@@ -9865,7 +9976,7 @@
         <v>225</v>
       </c>
       <c r="AD52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF52">
         <v>288</v>
@@ -9972,7 +10083,7 @@
         <v>231</v>
       </c>
       <c r="AD53" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF53">
         <v>312</v>
@@ -10079,7 +10190,7 @@
         <v>236</v>
       </c>
       <c r="AD54" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF54">
         <v>672</v>
@@ -10183,13 +10294,13 @@
         <v>41</v>
       </c>
       <c r="AC55" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="AD55" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE55" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF55">
         <v>360</v>
@@ -10299,7 +10410,7 @@
         <v>99</v>
       </c>
       <c r="AE56" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AF56">
         <v>528</v>
@@ -10406,7 +10517,7 @@
         <v>39</v>
       </c>
       <c r="AD57" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF57">
         <v>288</v>
@@ -10513,7 +10624,7 @@
         <v>39</v>
       </c>
       <c r="AD58" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF58">
         <v>288</v>
@@ -10620,7 +10731,7 @@
         <v>547</v>
       </c>
       <c r="AD59" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF59">
         <v>480</v>
@@ -10724,10 +10835,10 @@
         <v>41</v>
       </c>
       <c r="AC60" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="AD60" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF60">
         <v>840</v>
@@ -10834,10 +10945,10 @@
         <v>219</v>
       </c>
       <c r="AD61" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AE61" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF61">
         <v>324</v>
@@ -10944,7 +11055,7 @@
         <v>263</v>
       </c>
       <c r="AD62" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF62">
         <v>336</v>
@@ -11158,10 +11269,10 @@
         <v>41</v>
       </c>
       <c r="AD64" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AE64" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF64">
         <v>552</v>
@@ -11179,7 +11290,7 @@
         <v>1</v>
       </c>
       <c r="AK64" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="65" spans="1:36" x14ac:dyDescent="0.4">
@@ -11268,10 +11379,10 @@
         <v>41</v>
       </c>
       <c r="AC65" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="AD65" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF65">
         <v>360</v>
@@ -11378,7 +11489,7 @@
         <v>279</v>
       </c>
       <c r="AD66" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF66">
         <v>408</v>
@@ -11485,7 +11596,7 @@
         <v>48</v>
       </c>
       <c r="AD67" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AF67">
         <v>480</v>
@@ -11589,10 +11700,10 @@
         <v>41</v>
       </c>
       <c r="AC68" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="AD68" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AF68">
         <v>504</v>
@@ -11699,7 +11810,7 @@
         <v>290</v>
       </c>
       <c r="AD69" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AF69">
         <v>720</v>
@@ -11806,7 +11917,7 @@
         <v>120</v>
       </c>
       <c r="AD70" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF70">
         <v>216</v>
@@ -11913,7 +12024,7 @@
         <v>48</v>
       </c>
       <c r="AD71" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF71">
         <v>384</v>
@@ -12020,7 +12131,7 @@
         <v>48</v>
       </c>
       <c r="AD72" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AF72">
         <v>432</v>
@@ -12127,7 +12238,7 @@
         <v>219</v>
       </c>
       <c r="AD73" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AF73">
         <v>192</v>
@@ -12234,10 +12345,10 @@
         <v>48</v>
       </c>
       <c r="AD74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AE74" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AF74">
         <v>180</v>
@@ -12344,10 +12455,10 @@
         <v>48</v>
       </c>
       <c r="AD75" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AE75" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AF75">
         <v>144</v>
@@ -12454,10 +12565,10 @@
         <v>48</v>
       </c>
       <c r="AD76" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AE76" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AF76">
         <v>144</v>
@@ -12561,13 +12672,13 @@
         <v>41</v>
       </c>
       <c r="AC77" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="AD77" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AE77" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AF77">
         <v>576</v>
@@ -12674,7 +12785,7 @@
         <v>41</v>
       </c>
       <c r="AD78" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF78">
         <v>480</v>
@@ -12781,10 +12892,10 @@
         <v>290</v>
       </c>
       <c r="AD79" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE79" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AF79">
         <v>624</v>
@@ -12891,10 +13002,10 @@
         <v>106</v>
       </c>
       <c r="AD80" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE80" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AF80">
         <v>624</v>
@@ -13001,7 +13112,7 @@
         <v>327</v>
       </c>
       <c r="AD81" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AE81" t="s">
         <v>327</v>
@@ -13221,7 +13332,7 @@
         <v>59</v>
       </c>
       <c r="AE83" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AF83">
         <v>672</v>
@@ -13328,7 +13439,7 @@
         <v>41</v>
       </c>
       <c r="AD84" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF84">
         <v>288</v>
@@ -13435,7 +13546,7 @@
         <v>41</v>
       </c>
       <c r="AD85" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF85">
         <v>324</v>
@@ -13542,7 +13653,7 @@
         <v>41</v>
       </c>
       <c r="AD86" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AF86">
         <v>180</v>
@@ -13649,7 +13760,7 @@
         <v>41</v>
       </c>
       <c r="AD87" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF87">
         <v>288</v>
@@ -13863,7 +13974,7 @@
         <v>279</v>
       </c>
       <c r="AD89" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF89">
         <v>324</v>
@@ -13970,7 +14081,7 @@
         <v>41</v>
       </c>
       <c r="AD90" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF90">
         <v>432</v>
@@ -14077,10 +14188,10 @@
         <v>48</v>
       </c>
       <c r="AD91" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AE91" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF91">
         <v>288</v>
@@ -14187,10 +14298,10 @@
         <v>106</v>
       </c>
       <c r="AD92" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE92" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF92">
         <v>288</v>
@@ -14294,13 +14405,13 @@
         <v>41</v>
       </c>
       <c r="AC93" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="AD93" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE93" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF93">
         <v>288</v>
@@ -14410,7 +14521,7 @@
         <v>42</v>
       </c>
       <c r="AE94" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF94">
         <v>288</v>
@@ -14517,7 +14628,7 @@
         <v>41</v>
       </c>
       <c r="AD95" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF95">
         <v>216</v>
@@ -14624,7 +14735,7 @@
         <v>48</v>
       </c>
       <c r="AD96" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF96">
         <v>336</v>
@@ -14731,7 +14842,7 @@
         <v>48</v>
       </c>
       <c r="AD97" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF97">
         <v>720</v>
@@ -14838,7 +14949,7 @@
         <v>379</v>
       </c>
       <c r="AD98" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF98">
         <v>336</v>
@@ -14945,10 +15056,10 @@
         <v>379</v>
       </c>
       <c r="AD99" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AE99" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF99">
         <v>336</v>
@@ -15052,7 +15163,7 @@
         <v>41</v>
       </c>
       <c r="AC100" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AD100" t="s">
         <v>115</v>
@@ -15162,7 +15273,7 @@
         <v>48</v>
       </c>
       <c r="AD101" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF101">
         <v>336</v>
@@ -15269,7 +15380,7 @@
         <v>48</v>
       </c>
       <c r="AD102" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF102">
         <v>216</v>
@@ -15376,7 +15487,7 @@
         <v>395</v>
       </c>
       <c r="AD103" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF103">
         <v>576</v>
@@ -15483,10 +15594,10 @@
         <v>290</v>
       </c>
       <c r="AD104" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE104" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF104">
         <v>288</v>
@@ -15593,7 +15704,7 @@
         <v>48</v>
       </c>
       <c r="AD105" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF105">
         <v>312</v>
@@ -15611,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="AK105" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="106" spans="1:37" x14ac:dyDescent="0.4">
@@ -15703,7 +15814,7 @@
         <v>39</v>
       </c>
       <c r="AD106" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF106">
         <v>288</v>
@@ -15810,10 +15921,10 @@
         <v>48</v>
       </c>
       <c r="AD107" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AE107" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF107">
         <v>252</v>
@@ -15920,7 +16031,7 @@
         <v>41</v>
       </c>
       <c r="AD108" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF108">
         <v>504</v>
@@ -16348,7 +16459,7 @@
         <v>120</v>
       </c>
       <c r="AD112" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF112">
         <v>168</v>
@@ -16455,7 +16566,7 @@
         <v>41</v>
       </c>
       <c r="AD113" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AF113">
         <v>562</v>
@@ -16565,7 +16676,7 @@
         <v>99</v>
       </c>
       <c r="AE114" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AF114">
         <v>504</v>
@@ -16672,10 +16783,10 @@
         <v>286</v>
       </c>
       <c r="AD115" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AE115" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AF115">
         <v>240</v>
@@ -16782,10 +16893,10 @@
         <v>286</v>
       </c>
       <c r="AD116" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AE116" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AF116">
         <v>240</v>
@@ -16892,10 +17003,10 @@
         <v>286</v>
       </c>
       <c r="AD117" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AE117" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AF117">
         <v>240</v>
@@ -17002,10 +17113,10 @@
         <v>120</v>
       </c>
       <c r="AD118" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE118" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AF118">
         <v>240</v>
@@ -17112,10 +17223,10 @@
         <v>275</v>
       </c>
       <c r="AD119" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE119" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF119">
         <v>576</v>
@@ -17222,10 +17333,10 @@
         <v>279</v>
       </c>
       <c r="AD120" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE120" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF120">
         <v>624</v>
@@ -17332,10 +17443,10 @@
         <v>275</v>
       </c>
       <c r="AD121" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE121" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF121">
         <v>540</v>
@@ -17442,10 +17553,10 @@
         <v>456</v>
       </c>
       <c r="AD122" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE122" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF122">
         <v>504</v>
@@ -17552,10 +17663,10 @@
         <v>279</v>
       </c>
       <c r="AD123" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE123" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF123">
         <v>480</v>
@@ -17659,13 +17770,13 @@
         <v>41</v>
       </c>
       <c r="AC124" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AD124" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AE124" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF124">
         <v>864</v>
@@ -17772,10 +17883,10 @@
         <v>456</v>
       </c>
       <c r="AD125" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE125" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF125">
         <v>192</v>
@@ -17882,10 +17993,10 @@
         <v>469</v>
       </c>
       <c r="AD126" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE126" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF126">
         <v>288</v>
@@ -17992,10 +18103,10 @@
         <v>469</v>
       </c>
       <c r="AD127" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE127" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF127">
         <v>768</v>
@@ -18102,10 +18213,10 @@
         <v>469</v>
       </c>
       <c r="AD128" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AE128" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AF128">
         <v>288</v>
@@ -18212,10 +18323,10 @@
         <v>41</v>
       </c>
       <c r="AD129" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AE129" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF129">
         <v>288</v>
@@ -18319,10 +18430,10 @@
         <v>41</v>
       </c>
       <c r="AC130" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="AD130" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF130">
         <v>288</v>
@@ -18426,10 +18537,10 @@
         <v>41</v>
       </c>
       <c r="AC131" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="AD131" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF131">
         <v>480</v>
@@ -18536,7 +18647,7 @@
         <v>469</v>
       </c>
       <c r="AD132" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF132">
         <v>216</v>
@@ -18750,7 +18861,7 @@
         <v>41</v>
       </c>
       <c r="AD134" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF134">
         <v>480</v>
@@ -18857,7 +18968,7 @@
         <v>275</v>
       </c>
       <c r="AD135" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF135">
         <v>144</v>
@@ -18961,10 +19072,10 @@
         <v>41</v>
       </c>
       <c r="AC136" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="AD136" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AF136">
         <v>480</v>
@@ -19071,7 +19182,7 @@
         <v>507</v>
       </c>
       <c r="AD137" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF137">
         <v>288</v>
@@ -19178,7 +19289,7 @@
         <v>512</v>
       </c>
       <c r="AD138" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF138">
         <v>192</v>
@@ -19285,7 +19396,7 @@
         <v>516</v>
       </c>
       <c r="AD139" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF139">
         <v>576</v>
@@ -19392,7 +19503,7 @@
         <v>48</v>
       </c>
       <c r="AD140" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF140">
         <v>480</v>
@@ -19606,7 +19717,7 @@
         <v>469</v>
       </c>
       <c r="AD142" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF142">
         <v>816</v>
@@ -19713,7 +19824,7 @@
         <v>469</v>
       </c>
       <c r="AD143" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF143">
         <v>336</v>
@@ -19930,7 +20041,7 @@
         <v>469</v>
       </c>
       <c r="AD145" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF145">
         <v>672</v>
@@ -20144,7 +20255,7 @@
         <v>469</v>
       </c>
       <c r="AD147" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF147">
         <v>480</v>
@@ -20251,10 +20362,10 @@
         <v>547</v>
       </c>
       <c r="AD148" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AE148" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF148">
         <v>720</v>
@@ -20364,7 +20475,7 @@
         <v>59</v>
       </c>
       <c r="AE149" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF149">
         <v>720</v>
@@ -20471,10 +20582,10 @@
         <v>547</v>
       </c>
       <c r="AD150" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE150" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF150">
         <v>1152</v>
@@ -20581,7 +20692,7 @@
         <v>219</v>
       </c>
       <c r="AD151" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF151">
         <v>288</v>
@@ -20688,7 +20799,7 @@
         <v>558</v>
       </c>
       <c r="AD152" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF152">
         <v>288</v>
@@ -20795,7 +20906,7 @@
         <v>562</v>
       </c>
       <c r="AD153" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF153">
         <v>120</v>
@@ -21006,10 +21117,10 @@
         <v>41</v>
       </c>
       <c r="AC155" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="AD155" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF155">
         <v>216</v>
@@ -21223,10 +21334,10 @@
         <v>39</v>
       </c>
       <c r="AD157" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AE157" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="AF157">
         <v>900</v>
@@ -21333,10 +21444,10 @@
         <v>41</v>
       </c>
       <c r="AD158" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE158" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF158">
         <v>468</v>
@@ -21443,10 +21554,10 @@
         <v>41</v>
       </c>
       <c r="AD159" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE159" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF159">
         <v>288</v>
@@ -21553,10 +21664,10 @@
         <v>181</v>
       </c>
       <c r="AD160" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AE160" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF160">
         <v>384</v>
@@ -21663,7 +21774,7 @@
         <v>181</v>
       </c>
       <c r="AD161" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF161">
         <v>720</v>
@@ -21770,7 +21881,7 @@
         <v>286</v>
       </c>
       <c r="AD162" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF162">
         <v>540</v>
@@ -21877,7 +21988,7 @@
         <v>558</v>
       </c>
       <c r="AD163" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF163">
         <v>768</v>
@@ -21981,10 +22092,10 @@
         <v>119</v>
       </c>
       <c r="AC164" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="AD164" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF164">
         <v>768</v>
@@ -22091,7 +22202,7 @@
         <v>120</v>
       </c>
       <c r="AD165" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF165">
         <v>480</v>
@@ -22198,10 +22309,10 @@
         <v>286</v>
       </c>
       <c r="AD166" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AE166" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF166">
         <v>432</v>
@@ -22305,10 +22416,10 @@
         <v>41</v>
       </c>
       <c r="AC167" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AD167" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF167">
         <v>620</v>
@@ -22415,7 +22526,7 @@
         <v>41</v>
       </c>
       <c r="AD168" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF168">
         <v>312</v>
@@ -22522,7 +22633,7 @@
         <v>188</v>
       </c>
       <c r="AD169" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF169">
         <v>336</v>
@@ -22629,7 +22740,7 @@
         <v>120</v>
       </c>
       <c r="AD170" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF170">
         <v>768</v>
@@ -22736,7 +22847,7 @@
         <v>120</v>
       </c>
       <c r="AD171" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF171">
         <v>576</v>
@@ -22843,7 +22954,7 @@
         <v>48</v>
       </c>
       <c r="AD172" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF172">
         <v>720</v>
@@ -23057,7 +23168,7 @@
         <v>275</v>
       </c>
       <c r="AD174" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF174">
         <v>840</v>
@@ -23164,7 +23275,7 @@
         <v>130</v>
       </c>
       <c r="AD175" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF175">
         <v>1080</v>
@@ -23271,7 +23382,7 @@
         <v>181</v>
       </c>
       <c r="AD176" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF176">
         <v>240</v>
@@ -23375,10 +23486,10 @@
         <v>119</v>
       </c>
       <c r="AC177" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="AD177" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF177">
         <v>384</v>
@@ -23482,10 +23593,10 @@
         <v>41</v>
       </c>
       <c r="AC178" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="AD178" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF178">
         <v>216</v>
@@ -23592,7 +23703,7 @@
         <v>219</v>
       </c>
       <c r="AD179" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="AF179">
         <v>720</v>
@@ -23699,7 +23810,7 @@
         <v>469</v>
       </c>
       <c r="AD180" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF180">
         <v>408</v>
@@ -23806,7 +23917,7 @@
         <v>41</v>
       </c>
       <c r="AD181" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF181">
         <v>192</v>
@@ -23916,7 +24027,7 @@
         <v>99</v>
       </c>
       <c r="AE182" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF182">
         <v>780</v>
@@ -24020,13 +24131,13 @@
         <v>41</v>
       </c>
       <c r="AC183" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AD183" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AE183" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF183">
         <v>240</v>
@@ -24133,7 +24244,7 @@
         <v>219</v>
       </c>
       <c r="AD184" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF184">
         <v>288</v>
@@ -24151,7 +24262,7 @@
         <v>1</v>
       </c>
       <c r="AK184" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="185" spans="1:37" x14ac:dyDescent="0.4">
@@ -24243,7 +24354,7 @@
         <v>566</v>
       </c>
       <c r="AD185" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF185">
         <v>192</v>
@@ -24350,7 +24461,7 @@
         <v>507</v>
       </c>
       <c r="AD186" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF186">
         <v>480</v>
@@ -24564,7 +24675,7 @@
         <v>41</v>
       </c>
       <c r="AD188" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF188">
         <v>720</v>
@@ -24668,10 +24779,10 @@
         <v>41</v>
       </c>
       <c r="AC189" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="AD189" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF189">
         <v>288</v>
@@ -24778,7 +24889,7 @@
         <v>286</v>
       </c>
       <c r="AD190" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF190">
         <v>432</v>
@@ -24885,7 +24996,7 @@
         <v>681</v>
       </c>
       <c r="AD191" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF191">
         <v>576</v>
@@ -25206,7 +25317,7 @@
         <v>41</v>
       </c>
       <c r="AD194" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AF194">
         <v>480</v>
@@ -25313,7 +25424,7 @@
         <v>41</v>
       </c>
       <c r="AD195" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF195">
         <v>420</v>
@@ -25420,7 +25531,7 @@
         <v>41</v>
       </c>
       <c r="AD196" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF196">
         <v>192</v>
@@ -25527,7 +25638,7 @@
         <v>41</v>
       </c>
       <c r="AD197" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF197">
         <v>468</v>
@@ -25634,7 +25745,7 @@
         <v>41</v>
       </c>
       <c r="AD198" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF198">
         <v>384</v>
@@ -25741,7 +25852,7 @@
         <v>456</v>
       </c>
       <c r="AD199" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF199">
         <v>384</v>
@@ -25848,7 +25959,7 @@
         <v>41</v>
       </c>
       <c r="AD200" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF200">
         <v>432</v>
@@ -26062,7 +26173,7 @@
         <v>41</v>
       </c>
       <c r="AD202" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF202">
         <v>216</v>
@@ -26169,10 +26280,10 @@
         <v>41</v>
       </c>
       <c r="AD203" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE203" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF203">
         <v>192</v>
@@ -26279,7 +26390,7 @@
         <v>456</v>
       </c>
       <c r="AD204" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF204">
         <v>108</v>
@@ -26386,10 +26497,10 @@
         <v>192</v>
       </c>
       <c r="AD205" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AE205" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF205">
         <v>288</v>
@@ -26496,7 +26607,7 @@
         <v>41</v>
       </c>
       <c r="AD206" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF206">
         <v>504</v>
@@ -26603,7 +26714,7 @@
         <v>41</v>
       </c>
       <c r="AD207" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF207">
         <v>576</v>
@@ -26710,10 +26821,10 @@
         <v>456</v>
       </c>
       <c r="AD208" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE208" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF208">
         <v>360</v>
@@ -26820,7 +26931,7 @@
         <v>286</v>
       </c>
       <c r="AD209" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF209">
         <v>2112</v>
@@ -26927,7 +27038,7 @@
         <v>286</v>
       </c>
       <c r="AD210" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF210">
         <v>384</v>
@@ -27031,7 +27142,7 @@
         <v>41</v>
       </c>
       <c r="AC211" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AD211" t="s">
         <v>99</v>
@@ -27141,7 +27252,7 @@
         <v>746</v>
       </c>
       <c r="AD212" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF212">
         <v>384</v>
@@ -27245,13 +27356,13 @@
         <v>41</v>
       </c>
       <c r="AC213" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="AD213" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE213" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF213">
         <v>168</v>
@@ -27358,7 +27469,7 @@
         <v>753</v>
       </c>
       <c r="AD214" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF214">
         <v>720</v>
@@ -27465,7 +27576,7 @@
         <v>507</v>
       </c>
       <c r="AD215" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF215">
         <v>240</v>
@@ -27572,10 +27683,10 @@
         <v>469</v>
       </c>
       <c r="AD216" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE216" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF216">
         <v>384</v>
@@ -27682,10 +27793,10 @@
         <v>763</v>
       </c>
       <c r="AD217" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE217" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF217">
         <v>269</v>
@@ -27789,13 +27900,13 @@
         <v>119</v>
       </c>
       <c r="AC218" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AD218" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE218" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF218">
         <v>408</v>
@@ -27899,10 +28010,10 @@
         <v>41</v>
       </c>
       <c r="AC219" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="AD219" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AF219">
         <v>864</v>
@@ -28006,10 +28117,10 @@
         <v>41</v>
       </c>
       <c r="AC220" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="AD220" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AF220">
         <v>480</v>
@@ -28116,7 +28227,7 @@
         <v>286</v>
       </c>
       <c r="AD221" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF221">
         <v>336</v>
@@ -28223,7 +28334,7 @@
         <v>780</v>
       </c>
       <c r="AD222" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF222">
         <v>660</v>
@@ -28327,13 +28438,13 @@
         <v>41</v>
       </c>
       <c r="AC223" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="AD223" t="s">
         <v>99</v>
       </c>
       <c r="AE223" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF223">
         <v>600</v>
@@ -28440,7 +28551,7 @@
         <v>192</v>
       </c>
       <c r="AD224" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF224">
         <v>288</v>
@@ -28547,7 +28658,7 @@
         <v>286</v>
       </c>
       <c r="AD225" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF225">
         <v>540</v>
@@ -28654,7 +28765,7 @@
         <v>286</v>
       </c>
       <c r="AD226" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AF226">
         <v>900</v>
@@ -28761,7 +28872,7 @@
         <v>192</v>
       </c>
       <c r="AD227" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AF227">
         <v>1920</v>
@@ -28868,7 +28979,7 @@
         <v>456</v>
       </c>
       <c r="AD228" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AF228">
         <v>960</v>
@@ -28975,7 +29086,7 @@
         <v>130</v>
       </c>
       <c r="AD229" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF229">
         <v>660</v>
@@ -29079,13 +29190,13 @@
         <v>41</v>
       </c>
       <c r="AC230" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="AD230" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE230" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF230">
         <v>720</v>
@@ -29189,10 +29300,10 @@
         <v>41</v>
       </c>
       <c r="AC231" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="AD231" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF231">
         <v>432</v>
@@ -29299,7 +29410,7 @@
         <v>286</v>
       </c>
       <c r="AD232" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF232">
         <v>336</v>
@@ -29406,7 +29517,7 @@
         <v>469</v>
       </c>
       <c r="AD233" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF233">
         <v>360</v>
@@ -29513,7 +29624,7 @@
         <v>512</v>
       </c>
       <c r="AD234" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF234">
         <v>108</v>
@@ -29617,10 +29728,10 @@
         <v>41</v>
       </c>
       <c r="AC235" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AD235" t="s">
         <v>1115</v>
-      </c>
-      <c r="AD235" t="s">
-        <v>1116</v>
       </c>
       <c r="AF235">
         <v>756</v>
@@ -29727,7 +29838,7 @@
         <v>48</v>
       </c>
       <c r="AD236" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF236">
         <v>396</v>
@@ -29834,7 +29945,7 @@
         <v>828</v>
       </c>
       <c r="AD237" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF237">
         <v>720</v>
@@ -29941,7 +30052,7 @@
         <v>828</v>
       </c>
       <c r="AD238" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF238">
         <v>1248</v>
@@ -30048,7 +30159,7 @@
         <v>828</v>
       </c>
       <c r="AD239" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF239">
         <v>522</v>
@@ -30155,7 +30266,7 @@
         <v>828</v>
       </c>
       <c r="AD240" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF240">
         <v>1200</v>
@@ -30181,7 +30292,7 @@
         <v>839</v>
       </c>
       <c r="C241" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D241">
         <v>71</v>
@@ -30262,7 +30373,7 @@
         <v>840</v>
       </c>
       <c r="AD241" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF241">
         <v>540</v>
@@ -30369,7 +30480,7 @@
         <v>844</v>
       </c>
       <c r="AD242" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF242">
         <v>624</v>
@@ -30609,13 +30720,13 @@
         <v>852</v>
       </c>
       <c r="C245" t="s">
-        <v>853</v>
+        <v>1266</v>
       </c>
       <c r="D245">
         <v>66</v>
       </c>
       <c r="E245">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F245">
         <v>100</v>
@@ -30627,34 +30738,34 @@
         <v>80</v>
       </c>
       <c r="I245">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J245">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K245">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="L245">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="M245">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N245">
         <v>1</v>
       </c>
       <c r="O245">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="P245">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="Q245">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R245">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="S245">
         <v>10</v>
@@ -30687,19 +30798,19 @@
         <v>41</v>
       </c>
       <c r="AC245" t="s">
-        <v>379</v>
+        <v>1269</v>
       </c>
       <c r="AD245" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AE245" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF245">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="AG245" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AH245">
         <v>0</v>
@@ -30716,55 +30827,55 @@
         <v>4243</v>
       </c>
       <c r="B246" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C246" t="s">
-        <v>853</v>
+        <v>1267</v>
       </c>
       <c r="D246">
         <v>65</v>
       </c>
       <c r="E246">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F246">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G246">
         <v>125</v>
       </c>
       <c r="H246">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I246">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J246">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K246">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="L246">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M246">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N246">
         <v>1</v>
       </c>
       <c r="O246">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="P246">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="Q246">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R246">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="S246">
         <v>10</v>
@@ -30797,16 +30908,16 @@
         <v>41</v>
       </c>
       <c r="AC246" t="s">
-        <v>379</v>
+        <v>1269</v>
       </c>
       <c r="AD246" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AF246">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="AG246" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AH246">
         <v>0</v>
@@ -30823,10 +30934,10 @@
         <v>4244</v>
       </c>
       <c r="B247" t="s">
+        <v>856</v>
+      </c>
+      <c r="C247" t="s">
         <v>857</v>
-      </c>
-      <c r="C247" t="s">
-        <v>858</v>
       </c>
       <c r="D247">
         <v>56</v>
@@ -30904,7 +31015,7 @@
         <v>41</v>
       </c>
       <c r="AC247" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="AD247" t="s">
         <v>115</v>
@@ -30913,7 +31024,7 @@
         <v>480</v>
       </c>
       <c r="AG247" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AH247">
         <v>0</v>
@@ -30930,10 +31041,10 @@
         <v>4245</v>
       </c>
       <c r="B248" t="s">
+        <v>859</v>
+      </c>
+      <c r="C248" t="s">
         <v>860</v>
-      </c>
-      <c r="C248" t="s">
-        <v>861</v>
       </c>
       <c r="D248">
         <v>37</v>
@@ -31020,7 +31131,7 @@
         <v>432</v>
       </c>
       <c r="AG248" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AH248">
         <v>0</v>
@@ -31037,10 +31148,10 @@
         <v>4246</v>
       </c>
       <c r="B249" t="s">
+        <v>862</v>
+      </c>
+      <c r="C249" t="s">
         <v>863</v>
-      </c>
-      <c r="C249" t="s">
-        <v>864</v>
       </c>
       <c r="D249">
         <v>60</v>
@@ -31100,7 +31211,7 @@
         <v>229</v>
       </c>
       <c r="W249" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="X249">
         <v>1072</v>
@@ -31127,7 +31238,7 @@
         <v>312</v>
       </c>
       <c r="AG249" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="AH249">
         <v>0</v>
@@ -31144,10 +31255,10 @@
         <v>4247</v>
       </c>
       <c r="B250" t="s">
+        <v>866</v>
+      </c>
+      <c r="C250" t="s">
         <v>867</v>
-      </c>
-      <c r="C250" t="s">
-        <v>868</v>
       </c>
       <c r="D250">
         <v>67</v>
@@ -31234,7 +31345,7 @@
         <v>720</v>
       </c>
       <c r="AG250" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AH250">
         <v>0</v>
@@ -31251,10 +31362,10 @@
         <v>4248</v>
       </c>
       <c r="B251" t="s">
+        <v>869</v>
+      </c>
+      <c r="C251" t="s">
         <v>870</v>
-      </c>
-      <c r="C251" t="s">
-        <v>871</v>
       </c>
       <c r="D251">
         <v>64</v>
@@ -31341,7 +31452,7 @@
         <v>720</v>
       </c>
       <c r="AG251" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AH251">
         <v>0</v>
@@ -31358,10 +31469,10 @@
         <v>4249</v>
       </c>
       <c r="B252" t="s">
+        <v>872</v>
+      </c>
+      <c r="C252" t="s">
         <v>873</v>
-      </c>
-      <c r="C252" t="s">
-        <v>874</v>
       </c>
       <c r="D252">
         <v>59</v>
@@ -31421,7 +31532,7 @@
         <v>219</v>
       </c>
       <c r="W252" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="X252">
         <v>1260</v>
@@ -31442,16 +31553,16 @@
         <v>219</v>
       </c>
       <c r="AD252" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE252" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AF252">
         <v>672</v>
       </c>
       <c r="AG252" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AH252">
         <v>0</v>
@@ -31468,10 +31579,10 @@
         <v>4250</v>
       </c>
       <c r="B253" t="s">
+        <v>876</v>
+      </c>
+      <c r="C253" t="s">
         <v>877</v>
-      </c>
-      <c r="C253" t="s">
-        <v>878</v>
       </c>
       <c r="D253">
         <v>57</v>
@@ -31549,16 +31660,16 @@
         <v>41</v>
       </c>
       <c r="AC253" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="AD253" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF253">
         <v>540</v>
       </c>
       <c r="AG253" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AH253">
         <v>0</v>
@@ -31575,10 +31686,10 @@
         <v>4251</v>
       </c>
       <c r="B254" t="s">
+        <v>879</v>
+      </c>
+      <c r="C254" t="s">
         <v>880</v>
-      </c>
-      <c r="C254" t="s">
-        <v>881</v>
       </c>
       <c r="D254">
         <v>65</v>
@@ -31659,16 +31770,16 @@
         <v>641</v>
       </c>
       <c r="AD254" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE254" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF254">
         <v>384</v>
       </c>
       <c r="AG254" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="AH254">
         <v>0</v>
@@ -31685,10 +31796,10 @@
         <v>4252</v>
       </c>
       <c r="B255" t="s">
+        <v>882</v>
+      </c>
+      <c r="C255" t="s">
         <v>883</v>
-      </c>
-      <c r="C255" t="s">
-        <v>884</v>
       </c>
       <c r="D255">
         <v>72</v>
@@ -31769,13 +31880,13 @@
         <v>47</v>
       </c>
       <c r="AD255" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF255">
         <v>420</v>
       </c>
       <c r="AG255" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AH255">
         <v>0</v>
@@ -31792,10 +31903,10 @@
         <v>4253</v>
       </c>
       <c r="B256" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C256" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D256">
         <v>80</v>
@@ -31876,13 +31987,13 @@
         <v>47</v>
       </c>
       <c r="AD256" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF256">
         <v>420</v>
       </c>
       <c r="AG256" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="AH256">
         <v>0</v>
@@ -31899,10 +32010,10 @@
         <v>4254</v>
       </c>
       <c r="B257" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C257" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D257">
         <v>78</v>
@@ -31983,13 +32094,13 @@
         <v>47</v>
       </c>
       <c r="AD257" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF257">
         <v>420</v>
       </c>
       <c r="AG257" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="AH257">
         <v>0</v>
@@ -32006,10 +32117,10 @@
         <v>4255</v>
       </c>
       <c r="B258" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C258" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D258">
         <v>75</v>
@@ -32090,13 +32201,13 @@
         <v>47</v>
       </c>
       <c r="AD258" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF258">
         <v>420</v>
       </c>
       <c r="AG258" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="AH258">
         <v>0</v>
@@ -32113,10 +32224,10 @@
         <v>4256</v>
       </c>
       <c r="B259" t="s">
+        <v>891</v>
+      </c>
+      <c r="C259" t="s">
         <v>892</v>
-      </c>
-      <c r="C259" t="s">
-        <v>893</v>
       </c>
       <c r="D259">
         <v>25</v>
@@ -32197,13 +32308,13 @@
         <v>41</v>
       </c>
       <c r="AD259" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF259">
         <v>108</v>
       </c>
       <c r="AG259" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="AH259">
         <v>0</v>
@@ -32220,10 +32331,10 @@
         <v>4257</v>
       </c>
       <c r="B260" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C260" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D260">
         <v>28</v>
@@ -32283,7 +32394,7 @@
         <v>160</v>
       </c>
       <c r="W260" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="X260">
         <v>1248</v>
@@ -32304,13 +32415,13 @@
         <v>41</v>
       </c>
       <c r="AD260" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF260">
         <v>336</v>
       </c>
       <c r="AG260" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="AH260">
         <v>0</v>
@@ -32327,10 +32438,10 @@
         <v>4258</v>
       </c>
       <c r="B261" t="s">
+        <v>897</v>
+      </c>
+      <c r="C261" t="s">
         <v>898</v>
-      </c>
-      <c r="C261" t="s">
-        <v>899</v>
       </c>
       <c r="D261">
         <v>40</v>
@@ -32417,7 +32528,7 @@
         <v>1224</v>
       </c>
       <c r="AG261" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AH261">
         <v>0</v>
@@ -32434,10 +32545,10 @@
         <v>4259</v>
       </c>
       <c r="B262" t="s">
+        <v>900</v>
+      </c>
+      <c r="C262" t="s">
         <v>901</v>
-      </c>
-      <c r="C262" t="s">
-        <v>902</v>
       </c>
       <c r="D262">
         <v>42</v>
@@ -32518,13 +32629,13 @@
         <v>120</v>
       </c>
       <c r="AD262" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF262">
         <v>336</v>
       </c>
       <c r="AG262" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AH262">
         <v>0</v>
@@ -32541,10 +32652,10 @@
         <v>4260</v>
       </c>
       <c r="B263" t="s">
+        <v>903</v>
+      </c>
+      <c r="C263" t="s">
         <v>904</v>
-      </c>
-      <c r="C263" t="s">
-        <v>905</v>
       </c>
       <c r="D263">
         <v>25</v>
@@ -32625,16 +32736,16 @@
         <v>41</v>
       </c>
       <c r="AD263" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE263" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AF263">
         <v>384</v>
       </c>
       <c r="AG263" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AH263">
         <v>0</v>
@@ -32651,10 +32762,10 @@
         <v>4261</v>
       </c>
       <c r="B264" t="s">
+        <v>906</v>
+      </c>
+      <c r="C264" t="s">
         <v>907</v>
-      </c>
-      <c r="C264" t="s">
-        <v>908</v>
       </c>
       <c r="D264">
         <v>73</v>
@@ -32732,16 +32843,16 @@
         <v>119</v>
       </c>
       <c r="AC264" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="AD264" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF264">
         <v>312</v>
       </c>
       <c r="AG264" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AH264">
         <v>0</v>
@@ -32758,10 +32869,10 @@
         <v>4262</v>
       </c>
       <c r="B265" t="s">
+        <v>909</v>
+      </c>
+      <c r="C265" t="s">
         <v>910</v>
-      </c>
-      <c r="C265" t="s">
-        <v>911</v>
       </c>
       <c r="D265">
         <v>61</v>
@@ -32848,7 +32959,7 @@
         <v>288</v>
       </c>
       <c r="AG265" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="AH265">
         <v>0</v>
@@ -32865,10 +32976,10 @@
         <v>4263</v>
       </c>
       <c r="B266" t="s">
+        <v>912</v>
+      </c>
+      <c r="C266" t="s">
         <v>913</v>
-      </c>
-      <c r="C266" t="s">
-        <v>914</v>
       </c>
       <c r="D266">
         <v>77</v>
@@ -32946,16 +33057,16 @@
         <v>119</v>
       </c>
       <c r="AC266" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="AD266" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF266">
         <v>252</v>
       </c>
       <c r="AG266" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="AH266">
         <v>0</v>
@@ -32972,10 +33083,10 @@
         <v>4264</v>
       </c>
       <c r="B267" t="s">
+        <v>915</v>
+      </c>
+      <c r="C267" t="s">
         <v>916</v>
-      </c>
-      <c r="C267" t="s">
-        <v>917</v>
       </c>
       <c r="D267">
         <v>40</v>
@@ -33056,13 +33167,13 @@
         <v>41</v>
       </c>
       <c r="AD267" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF267">
         <v>432</v>
       </c>
       <c r="AG267" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="AH267">
         <v>0</v>
@@ -33079,10 +33190,10 @@
         <v>4265</v>
       </c>
       <c r="B268" t="s">
+        <v>918</v>
+      </c>
+      <c r="C268" t="s">
         <v>919</v>
-      </c>
-      <c r="C268" t="s">
-        <v>920</v>
       </c>
       <c r="D268">
         <v>74</v>
@@ -33160,19 +33271,19 @@
         <v>41</v>
       </c>
       <c r="AC268" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AD268" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE268" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF268">
         <v>720</v>
       </c>
       <c r="AG268" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="AH268">
         <v>0</v>
@@ -33189,10 +33300,10 @@
         <v>4266</v>
       </c>
       <c r="B269" t="s">
+        <v>922</v>
+      </c>
+      <c r="C269" t="s">
         <v>923</v>
-      </c>
-      <c r="C269" t="s">
-        <v>924</v>
       </c>
       <c r="D269">
         <v>25</v>
@@ -33273,13 +33384,13 @@
         <v>41</v>
       </c>
       <c r="AD269" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF269">
         <v>468</v>
       </c>
       <c r="AG269" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="AH269">
         <v>0</v>
@@ -33296,10 +33407,10 @@
         <v>4267</v>
       </c>
       <c r="B270" t="s">
+        <v>925</v>
+      </c>
+      <c r="C270" t="s">
         <v>926</v>
-      </c>
-      <c r="C270" t="s">
-        <v>927</v>
       </c>
       <c r="D270">
         <v>42</v>
@@ -33380,13 +33491,13 @@
         <v>516</v>
       </c>
       <c r="AD270" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF270">
         <v>540</v>
       </c>
       <c r="AG270" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AH270">
         <v>0</v>
@@ -33403,10 +33514,10 @@
         <v>4268</v>
       </c>
       <c r="B271" t="s">
+        <v>928</v>
+      </c>
+      <c r="C271" t="s">
         <v>929</v>
-      </c>
-      <c r="C271" t="s">
-        <v>930</v>
       </c>
       <c r="D271">
         <v>28</v>
@@ -33487,13 +33598,13 @@
         <v>41</v>
       </c>
       <c r="AD271" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF271">
         <v>336</v>
       </c>
       <c r="AG271" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="AH271">
         <v>0</v>
@@ -33510,10 +33621,10 @@
         <v>4269</v>
       </c>
       <c r="B272" t="s">
+        <v>931</v>
+      </c>
+      <c r="C272" t="s">
         <v>932</v>
-      </c>
-      <c r="C272" t="s">
-        <v>933</v>
       </c>
       <c r="D272">
         <v>30</v>
@@ -33600,7 +33711,7 @@
         <v>288</v>
       </c>
       <c r="AG272" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AH272">
         <v>0</v>
@@ -33617,10 +33728,10 @@
         <v>4270</v>
       </c>
       <c r="B273" t="s">
+        <v>934</v>
+      </c>
+      <c r="C273" t="s">
         <v>935</v>
-      </c>
-      <c r="C273" t="s">
-        <v>936</v>
       </c>
       <c r="D273">
         <v>31</v>
@@ -33701,13 +33812,13 @@
         <v>41</v>
       </c>
       <c r="AD273" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF273">
         <v>252</v>
       </c>
       <c r="AG273" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="AH273">
         <v>0</v>
@@ -33724,10 +33835,10 @@
         <v>4271</v>
       </c>
       <c r="B274" t="s">
+        <v>937</v>
+      </c>
+      <c r="C274" t="s">
         <v>938</v>
-      </c>
-      <c r="C274" t="s">
-        <v>939</v>
       </c>
       <c r="D274">
         <v>61</v>
@@ -33787,7 +33898,7 @@
         <v>160</v>
       </c>
       <c r="W274" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="X274">
         <v>1100</v>
@@ -33808,13 +33919,13 @@
         <v>181</v>
       </c>
       <c r="AD274" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF274">
         <v>576</v>
       </c>
       <c r="AG274" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AH274">
         <v>0</v>
@@ -33831,10 +33942,10 @@
         <v>4272</v>
       </c>
       <c r="B275" t="s">
+        <v>941</v>
+      </c>
+      <c r="C275" t="s">
         <v>942</v>
-      </c>
-      <c r="C275" t="s">
-        <v>943</v>
       </c>
       <c r="D275">
         <v>65</v>
@@ -33915,13 +34026,13 @@
         <v>516</v>
       </c>
       <c r="AD275" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF275">
         <v>576</v>
       </c>
       <c r="AG275" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="AH275">
         <v>0</v>
@@ -33938,10 +34049,10 @@
         <v>4273</v>
       </c>
       <c r="B276" t="s">
+        <v>944</v>
+      </c>
+      <c r="C276" t="s">
         <v>945</v>
-      </c>
-      <c r="C276" t="s">
-        <v>946</v>
       </c>
       <c r="D276">
         <v>61</v>
@@ -34022,13 +34133,13 @@
         <v>41</v>
       </c>
       <c r="AD276" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AF276">
         <v>480</v>
       </c>
       <c r="AG276" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="AH276">
         <v>0</v>
@@ -34045,10 +34156,10 @@
         <v>4274</v>
       </c>
       <c r="B277" t="s">
+        <v>947</v>
+      </c>
+      <c r="C277" t="s">
         <v>948</v>
-      </c>
-      <c r="C277" t="s">
-        <v>949</v>
       </c>
       <c r="D277">
         <v>65</v>
@@ -34129,13 +34240,13 @@
         <v>746</v>
       </c>
       <c r="AD277" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF277">
         <v>900</v>
       </c>
       <c r="AG277" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AH277">
         <v>0</v>
@@ -34152,10 +34263,10 @@
         <v>4275</v>
       </c>
       <c r="B278" t="s">
+        <v>950</v>
+      </c>
+      <c r="C278" t="s">
         <v>951</v>
-      </c>
-      <c r="C278" t="s">
-        <v>952</v>
       </c>
       <c r="D278">
         <v>61</v>
@@ -34236,13 +34347,13 @@
         <v>516</v>
       </c>
       <c r="AD278" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF278">
         <v>432</v>
       </c>
       <c r="AG278" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AH278">
         <v>0</v>
@@ -34259,10 +34370,10 @@
         <v>4276</v>
       </c>
       <c r="B279" t="s">
+        <v>953</v>
+      </c>
+      <c r="C279" t="s">
         <v>954</v>
-      </c>
-      <c r="C279" t="s">
-        <v>955</v>
       </c>
       <c r="D279">
         <v>72</v>
@@ -34343,16 +34454,16 @@
         <v>746</v>
       </c>
       <c r="AD279" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AE279" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF279">
         <v>288</v>
       </c>
       <c r="AG279" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AH279">
         <v>0</v>
@@ -34369,10 +34480,10 @@
         <v>4277</v>
       </c>
       <c r="B280" t="s">
+        <v>956</v>
+      </c>
+      <c r="C280" t="s">
         <v>957</v>
-      </c>
-      <c r="C280" t="s">
-        <v>958</v>
       </c>
       <c r="D280">
         <v>79</v>
@@ -34453,13 +34564,13 @@
         <v>641</v>
       </c>
       <c r="AD280" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF280">
         <v>1080</v>
       </c>
       <c r="AG280" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AH280">
         <v>0</v>
@@ -34476,10 +34587,10 @@
         <v>4278</v>
       </c>
       <c r="B281" t="s">
+        <v>959</v>
+      </c>
+      <c r="C281" t="s">
         <v>960</v>
-      </c>
-      <c r="C281" t="s">
-        <v>961</v>
       </c>
       <c r="D281">
         <v>45</v>
@@ -34560,13 +34671,13 @@
         <v>41</v>
       </c>
       <c r="AD281" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF281">
         <v>384</v>
       </c>
       <c r="AG281" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="AH281">
         <v>0</v>
@@ -34583,10 +34694,10 @@
         <v>4279</v>
       </c>
       <c r="B282" t="s">
+        <v>962</v>
+      </c>
+      <c r="C282" t="s">
         <v>963</v>
-      </c>
-      <c r="C282" t="s">
-        <v>964</v>
       </c>
       <c r="D282">
         <v>37</v>
@@ -34667,13 +34778,13 @@
         <v>48</v>
       </c>
       <c r="AD282" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF282">
         <v>540</v>
       </c>
       <c r="AG282" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="AH282">
         <v>0</v>
@@ -34690,10 +34801,10 @@
         <v>4280</v>
       </c>
       <c r="B283" t="s">
+        <v>965</v>
+      </c>
+      <c r="C283" t="s">
         <v>966</v>
-      </c>
-      <c r="C283" t="s">
-        <v>967</v>
       </c>
       <c r="D283">
         <v>60</v>
@@ -34771,10 +34882,10 @@
         <v>41</v>
       </c>
       <c r="AC283" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="AD283" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AE283" t="s">
         <v>327</v>
@@ -34783,7 +34894,7 @@
         <v>720</v>
       </c>
       <c r="AG283" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="AH283">
         <v>0</v>
@@ -34800,10 +34911,10 @@
         <v>4281</v>
       </c>
       <c r="B284" t="s">
+        <v>968</v>
+      </c>
+      <c r="C284" t="s">
         <v>969</v>
-      </c>
-      <c r="C284" t="s">
-        <v>970</v>
       </c>
       <c r="D284">
         <v>34</v>
@@ -34890,7 +35001,7 @@
         <v>696</v>
       </c>
       <c r="AG284" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AH284">
         <v>0</v>
@@ -34907,10 +35018,10 @@
         <v>4282</v>
       </c>
       <c r="B285" t="s">
+        <v>971</v>
+      </c>
+      <c r="C285" t="s">
         <v>972</v>
-      </c>
-      <c r="C285" t="s">
-        <v>973</v>
       </c>
       <c r="D285">
         <v>45</v>
@@ -34988,7 +35099,7 @@
         <v>41</v>
       </c>
       <c r="AC285" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="AD285" t="s">
         <v>115</v>
@@ -35000,7 +35111,7 @@
         <v>936</v>
       </c>
       <c r="AG285" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="AH285">
         <v>0</v>
@@ -35017,10 +35128,10 @@
         <v>4283</v>
       </c>
       <c r="B286" t="s">
+        <v>974</v>
+      </c>
+      <c r="C286" t="s">
         <v>975</v>
-      </c>
-      <c r="C286" t="s">
-        <v>976</v>
       </c>
       <c r="D286">
         <v>70</v>
@@ -35110,7 +35221,7 @@
         <v>384</v>
       </c>
       <c r="AG286" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AH286">
         <v>0</v>
@@ -35127,10 +35238,10 @@
         <v>4284</v>
       </c>
       <c r="B287" t="s">
+        <v>977</v>
+      </c>
+      <c r="C287" t="s">
         <v>978</v>
-      </c>
-      <c r="C287" t="s">
-        <v>979</v>
       </c>
       <c r="D287">
         <v>1</v>
@@ -35217,7 +35328,7 @@
         <v>0</v>
       </c>
       <c r="AG287" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AH287">
         <v>0</v>
@@ -35229,7 +35340,7 @@
         <v>1</v>
       </c>
       <c r="AK287" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="288" spans="1:37" x14ac:dyDescent="0.4">
@@ -35237,10 +35348,10 @@
         <v>4285</v>
       </c>
       <c r="B288" t="s">
+        <v>980</v>
+      </c>
+      <c r="C288" t="s">
         <v>981</v>
-      </c>
-      <c r="C288" t="s">
-        <v>982</v>
       </c>
       <c r="D288">
         <v>1</v>
@@ -35321,16 +35432,16 @@
         <v>41</v>
       </c>
       <c r="AD288" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="AE288" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF288">
         <v>216</v>
       </c>
       <c r="AG288" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="AH288">
         <v>0</v>
@@ -35342,7 +35453,7 @@
         <v>1</v>
       </c>
       <c r="AK288" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="289" spans="1:37" x14ac:dyDescent="0.4">
@@ -35350,10 +35461,10 @@
         <v>4286</v>
       </c>
       <c r="B289" t="s">
+        <v>984</v>
+      </c>
+      <c r="C289" t="s">
         <v>985</v>
-      </c>
-      <c r="C289" t="s">
-        <v>986</v>
       </c>
       <c r="D289">
         <v>99</v>
@@ -35431,19 +35542,19 @@
         <v>119</v>
       </c>
       <c r="AC289" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="AD289" t="s">
         <v>99</v>
       </c>
       <c r="AE289" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF289">
         <v>504</v>
       </c>
       <c r="AG289" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AH289">
         <v>0</v>
@@ -35460,10 +35571,10 @@
         <v>4287</v>
       </c>
       <c r="B290" t="s">
+        <v>987</v>
+      </c>
+      <c r="C290" t="s">
         <v>988</v>
-      </c>
-      <c r="C290" t="s">
-        <v>989</v>
       </c>
       <c r="D290">
         <v>99</v>
@@ -35550,7 +35661,7 @@
         <v>504</v>
       </c>
       <c r="AG290" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AH290">
         <v>0</v>
@@ -35567,10 +35678,10 @@
         <v>4288</v>
       </c>
       <c r="B291" t="s">
+        <v>990</v>
+      </c>
+      <c r="C291" t="s">
         <v>991</v>
-      </c>
-      <c r="C291" t="s">
-        <v>992</v>
       </c>
       <c r="D291">
         <v>43</v>
@@ -35651,13 +35762,13 @@
         <v>48</v>
       </c>
       <c r="AD291" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AF291">
         <v>384</v>
       </c>
       <c r="AG291" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="AH291">
         <v>0</v>
@@ -35674,10 +35785,10 @@
         <v>4289</v>
       </c>
       <c r="B292" t="s">
+        <v>993</v>
+      </c>
+      <c r="C292" t="s">
         <v>994</v>
-      </c>
-      <c r="C292" t="s">
-        <v>995</v>
       </c>
       <c r="D292">
         <v>69</v>
@@ -35764,7 +35875,7 @@
         <v>480</v>
       </c>
       <c r="AG292" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="AH292">
         <v>0</v>
@@ -35781,10 +35892,10 @@
         <v>4290</v>
       </c>
       <c r="B293" t="s">
+        <v>996</v>
+      </c>
+      <c r="C293" t="s">
         <v>997</v>
-      </c>
-      <c r="C293" t="s">
-        <v>998</v>
       </c>
       <c r="D293">
         <v>51</v>
@@ -35865,13 +35976,13 @@
         <v>41</v>
       </c>
       <c r="AD293" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF293">
         <v>576</v>
       </c>
       <c r="AG293" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="AH293">
         <v>0</v>
@@ -35888,10 +35999,10 @@
         <v>4291</v>
       </c>
       <c r="B294" t="s">
+        <v>999</v>
+      </c>
+      <c r="C294" t="s">
         <v>1000</v>
-      </c>
-      <c r="C294" t="s">
-        <v>1001</v>
       </c>
       <c r="D294">
         <v>40</v>
@@ -35978,7 +36089,7 @@
         <v>432</v>
       </c>
       <c r="AG294" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="AH294">
         <v>0</v>
@@ -35995,10 +36106,10 @@
         <v>4292</v>
       </c>
       <c r="B295" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C295" t="s">
         <v>1003</v>
-      </c>
-      <c r="C295" t="s">
-        <v>1004</v>
       </c>
       <c r="D295">
         <v>65</v>
@@ -36079,13 +36190,13 @@
         <v>41</v>
       </c>
       <c r="AD295" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AF295">
         <v>624</v>
       </c>
       <c r="AG295" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AH295">
         <v>0</v>
@@ -36102,10 +36213,10 @@
         <v>4293</v>
       </c>
       <c r="B296" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C296" t="s">
         <v>1006</v>
-      </c>
-      <c r="C296" t="s">
-        <v>1007</v>
       </c>
       <c r="D296">
         <v>47</v>
@@ -36192,7 +36303,7 @@
         <v>480</v>
       </c>
       <c r="AG296" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AH296">
         <v>0</v>
@@ -36209,10 +36320,10 @@
         <v>4294</v>
       </c>
       <c r="B297" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C297" t="s">
         <v>1009</v>
-      </c>
-      <c r="C297" t="s">
-        <v>1010</v>
       </c>
       <c r="D297">
         <v>71</v>
@@ -36299,7 +36410,7 @@
         <v>425</v>
       </c>
       <c r="AG297" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AH297">
         <v>0</v>
@@ -36316,10 +36427,10 @@
         <v>4295</v>
       </c>
       <c r="B298" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C298" t="s">
         <v>1012</v>
-      </c>
-      <c r="C298" t="s">
-        <v>1013</v>
       </c>
       <c r="D298">
         <v>43</v>
@@ -36400,13 +36511,13 @@
         <v>41</v>
       </c>
       <c r="AD298" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AF298">
         <v>672</v>
       </c>
       <c r="AG298" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AH298">
         <v>0</v>
@@ -36423,10 +36534,10 @@
         <v>4296</v>
       </c>
       <c r="B299" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C299" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D299">
         <v>61</v>
@@ -36507,16 +36618,16 @@
         <v>456</v>
       </c>
       <c r="AD299" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE299" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF299">
         <v>540</v>
       </c>
       <c r="AG299" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="AH299">
         <v>0</v>
@@ -36533,10 +36644,10 @@
         <v>4297</v>
       </c>
       <c r="B300" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C300" t="s">
         <v>1017</v>
-      </c>
-      <c r="C300" t="s">
-        <v>1018</v>
       </c>
       <c r="D300">
         <v>46</v>
@@ -36614,7 +36725,7 @@
         <v>41</v>
       </c>
       <c r="AC300" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="AD300" t="s">
         <v>42</v>
@@ -36623,7 +36734,7 @@
         <v>624</v>
       </c>
       <c r="AG300" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="AH300">
         <v>0</v>
@@ -36640,10 +36751,10 @@
         <v>4298</v>
       </c>
       <c r="B301" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C301" t="s">
         <v>1175</v>
-      </c>
-      <c r="C301" t="s">
-        <v>1176</v>
       </c>
       <c r="D301">
         <v>99</v>
@@ -36730,7 +36841,7 @@
         <v>200</v>
       </c>
       <c r="AG301" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AH301">
         <v>0</v>
@@ -36742,7 +36853,7 @@
         <v>1</v>
       </c>
       <c r="AK301" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="302" spans="1:37" x14ac:dyDescent="0.4">
@@ -36750,10 +36861,10 @@
         <v>4299</v>
       </c>
       <c r="B302" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C302" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D302">
         <v>56</v>
@@ -36834,16 +36945,16 @@
         <v>181</v>
       </c>
       <c r="AD302" t="s">
-        <v>42</v>
+        <v>1194</v>
       </c>
       <c r="AE302" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AF302">
         <v>825</v>
       </c>
       <c r="AG302" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="AH302">
         <v>0</v>
@@ -36857,52 +36968,52 @@
     </row>
     <row r="303" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A303">
-        <v>5000</v>
+        <v>4300</v>
       </c>
       <c r="B303" t="s">
-        <v>44</v>
+        <v>1238</v>
       </c>
       <c r="C303" t="s">
-        <v>37</v>
+        <v>1240</v>
       </c>
       <c r="D303">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="E303">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="F303">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G303">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H303">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I303">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J303">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="K303">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L303">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M303">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N303">
         <v>1</v>
       </c>
       <c r="O303">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="P303">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="Q303">
         <v>100</v>
@@ -36917,40 +37028,40 @@
         <v>12</v>
       </c>
       <c r="U303" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="V303" t="s">
-        <v>39</v>
+        <v>219</v>
       </c>
       <c r="W303" t="s">
-        <v>40</v>
+        <v>619</v>
       </c>
       <c r="X303">
-        <v>1872</v>
+        <v>1216</v>
       </c>
       <c r="Y303">
-        <v>480</v>
+        <v>432</v>
       </c>
       <c r="Z303">
-        <v>672</v>
+        <v>816</v>
       </c>
       <c r="AA303">
-        <v>400</v>
+        <v>165</v>
       </c>
       <c r="AB303" t="s">
         <v>41</v>
       </c>
       <c r="AC303" t="s">
-        <v>39</v>
+        <v>1113</v>
       </c>
       <c r="AD303" t="s">
-        <v>1116</v>
+        <v>1194</v>
       </c>
       <c r="AF303">
-        <v>288</v>
+        <v>850</v>
       </c>
       <c r="AG303" t="s">
-        <v>43</v>
+        <v>1239</v>
       </c>
       <c r="AH303">
         <v>0</v>
@@ -36959,63 +37070,63 @@
         <v>0.5</v>
       </c>
       <c r="AJ303">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A304">
-        <v>6000</v>
+        <v>4301</v>
       </c>
       <c r="B304" t="s">
-        <v>1092</v>
+        <v>1241</v>
       </c>
       <c r="C304" t="s">
-        <v>565</v>
+        <v>1243</v>
       </c>
       <c r="D304">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E304">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="F304">
         <v>100</v>
       </c>
       <c r="G304">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H304">
         <v>100</v>
       </c>
       <c r="I304">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J304">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="K304">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L304">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M304">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N304">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O304">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="P304">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="Q304">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R304">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S304">
         <v>10</v>
@@ -37030,34 +37141,34 @@
         <v>219</v>
       </c>
       <c r="W304" t="s">
-        <v>274</v>
+        <v>511</v>
       </c>
       <c r="X304">
-        <v>1276</v>
+        <v>864</v>
       </c>
       <c r="Y304">
-        <v>288</v>
+        <v>476</v>
       </c>
       <c r="Z304">
-        <v>576</v>
+        <v>1252</v>
       </c>
       <c r="AA304">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AB304" t="s">
         <v>119</v>
       </c>
       <c r="AC304" t="s">
-        <v>566</v>
+        <v>1244</v>
       </c>
       <c r="AD304" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF304">
-        <v>180</v>
+        <v>400</v>
       </c>
       <c r="AG304" t="s">
-        <v>567</v>
+        <v>1242</v>
       </c>
       <c r="AH304">
         <v>0</v>
@@ -37068,22 +37179,19 @@
       <c r="AJ304">
         <v>1</v>
       </c>
-      <c r="AK304" t="s">
-        <v>1093</v>
-      </c>
     </row>
     <row r="305" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A305">
-        <v>6001</v>
+        <v>4302</v>
       </c>
       <c r="B305" t="s">
-        <v>1101</v>
+        <v>1211</v>
       </c>
       <c r="C305" t="s">
-        <v>77</v>
+        <v>1223</v>
       </c>
       <c r="D305">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="E305">
         <v>100</v>
@@ -37095,7 +37203,7 @@
         <v>100</v>
       </c>
       <c r="H305">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I305">
         <v>100</v>
@@ -37113,7 +37221,7 @@
         <v>10</v>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O305">
         <v>100</v>
@@ -37122,78 +37230,78 @@
         <v>100</v>
       </c>
       <c r="Q305">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S305">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T305">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U305" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="V305" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="W305" t="s">
         <v>619</v>
       </c>
       <c r="X305">
-        <v>701</v>
+        <v>1306</v>
       </c>
       <c r="Y305">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="Z305">
-        <v>1</v>
+        <v>1056</v>
       </c>
       <c r="AA305">
-        <v>-1</v>
+        <v>155</v>
       </c>
       <c r="AB305" t="s">
         <v>41</v>
       </c>
       <c r="AC305" t="s">
-        <v>1088</v>
+        <v>1113</v>
       </c>
       <c r="AD305" t="s">
-        <v>59</v>
+        <v>1118</v>
       </c>
       <c r="AF305">
-        <v>288</v>
+        <v>576</v>
       </c>
       <c r="AG305" t="s">
-        <v>79</v>
+        <v>1212</v>
       </c>
       <c r="AH305">
         <v>0</v>
       </c>
       <c r="AI305">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AJ305">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A306">
-        <v>6002</v>
+        <v>4303</v>
       </c>
       <c r="B306" t="s">
-        <v>1102</v>
+        <v>1213</v>
       </c>
       <c r="C306" t="s">
-        <v>1103</v>
+        <v>1224</v>
       </c>
       <c r="D306">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="E306">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F306">
         <v>100</v>
@@ -37214,13 +37322,13 @@
         <v>100</v>
       </c>
       <c r="L306">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M306">
         <v>10</v>
       </c>
       <c r="N306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O306">
         <v>100</v>
@@ -37229,13 +37337,13 @@
         <v>100</v>
       </c>
       <c r="Q306">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R306">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S306">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T306">
         <v>12</v>
@@ -37244,37 +37352,37 @@
         <v>38</v>
       </c>
       <c r="V306" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="W306" t="s">
         <v>619</v>
       </c>
       <c r="X306">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="Y306">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="Z306">
-        <v>288</v>
+        <v>600</v>
       </c>
       <c r="AA306">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="AB306" t="s">
         <v>41</v>
       </c>
       <c r="AC306" t="s">
-        <v>1087</v>
+        <v>1113</v>
       </c>
       <c r="AD306" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AF306">
-        <v>504</v>
+        <v>420</v>
       </c>
       <c r="AG306" t="s">
-        <v>283</v>
+        <v>1214</v>
       </c>
       <c r="AH306">
         <v>0</v>
@@ -37283,39 +37391,36 @@
         <v>0.5</v>
       </c>
       <c r="AJ306">
-        <v>0.7</v>
-      </c>
-      <c r="AK306" t="s">
-        <v>1104</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A307">
-        <v>6003</v>
+        <v>4304</v>
       </c>
       <c r="B307" t="s">
-        <v>1121</v>
+        <v>1245</v>
       </c>
       <c r="C307" t="s">
-        <v>1122</v>
+        <v>1247</v>
       </c>
       <c r="D307">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E307">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="F307">
         <v>100</v>
       </c>
       <c r="G307">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H307">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I307">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J307">
         <v>100</v>
@@ -37324,19 +37429,19 @@
         <v>100</v>
       </c>
       <c r="L307">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="M307">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N307">
         <v>1</v>
       </c>
       <c r="O307">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P307">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="Q307">
         <v>100</v>
@@ -37351,43 +37456,40 @@
         <v>12</v>
       </c>
       <c r="U307" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="V307" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="W307" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="X307">
-        <v>902</v>
+        <v>1000</v>
       </c>
       <c r="Y307">
-        <v>432</v>
+        <v>384</v>
       </c>
       <c r="Z307">
-        <v>648</v>
+        <v>600</v>
       </c>
       <c r="AA307">
         <v>150</v>
       </c>
       <c r="AB307" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="AC307" t="s">
-        <v>120</v>
+        <v>1113</v>
       </c>
       <c r="AD307" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AE307" t="s">
-        <v>1204</v>
+        <v>1118</v>
       </c>
       <c r="AF307">
-        <v>216</v>
+        <v>1000</v>
       </c>
       <c r="AG307" t="s">
-        <v>1123</v>
+        <v>1246</v>
       </c>
       <c r="AH307">
         <v>0</v>
@@ -37401,16 +37503,16 @@
     </row>
     <row r="308" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A308">
-        <v>6004</v>
+        <v>4305</v>
       </c>
       <c r="B308" t="s">
-        <v>1124</v>
+        <v>1248</v>
       </c>
       <c r="C308" t="s">
-        <v>1125</v>
+        <v>1250</v>
       </c>
       <c r="D308">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E308">
         <v>100</v>
@@ -37419,13 +37521,13 @@
         <v>100</v>
       </c>
       <c r="G308">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H308">
         <v>100</v>
       </c>
       <c r="I308">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="J308">
         <v>100</v>
@@ -37440,13 +37542,13 @@
         <v>10</v>
       </c>
       <c r="N308">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O308">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="P308">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Q308">
         <v>100</v>
@@ -37464,37 +37566,37 @@
         <v>38</v>
       </c>
       <c r="V308" t="s">
-        <v>53</v>
+        <v>469</v>
       </c>
       <c r="W308" t="s">
-        <v>40</v>
+        <v>470</v>
       </c>
       <c r="X308">
-        <v>1540</v>
+        <v>2612</v>
       </c>
       <c r="Y308">
-        <v>576</v>
+        <v>288</v>
       </c>
       <c r="Z308">
-        <v>720</v>
+        <v>912</v>
       </c>
       <c r="AA308">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="AB308" t="s">
         <v>41</v>
       </c>
       <c r="AC308" t="s">
-        <v>41</v>
+        <v>1105</v>
       </c>
       <c r="AD308" t="s">
-        <v>1118</v>
+        <v>1194</v>
       </c>
       <c r="AF308">
-        <v>324</v>
+        <v>950</v>
       </c>
       <c r="AG308" t="s">
-        <v>1126</v>
+        <v>1249</v>
       </c>
       <c r="AH308">
         <v>0</v>
@@ -37508,16 +37610,16 @@
     </row>
     <row r="309" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A309">
-        <v>6005</v>
+        <v>4306</v>
       </c>
       <c r="B309" t="s">
-        <v>1132</v>
+        <v>1251</v>
       </c>
       <c r="C309" t="s">
-        <v>1133</v>
+        <v>1253</v>
       </c>
       <c r="D309">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E309">
         <v>100</v>
@@ -37532,13 +37634,13 @@
         <v>100</v>
       </c>
       <c r="I309">
+        <v>100</v>
+      </c>
+      <c r="J309">
         <v>140</v>
       </c>
-      <c r="J309">
-        <v>100</v>
-      </c>
       <c r="K309">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="L309">
         <v>100</v>
@@ -37547,16 +37649,16 @@
         <v>10</v>
       </c>
       <c r="N309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P309">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="Q309">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="R309">
         <v>100</v>
@@ -37568,40 +37670,43 @@
         <v>12</v>
       </c>
       <c r="U309" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="V309" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="W309" t="s">
-        <v>49</v>
+        <v>249</v>
       </c>
       <c r="X309">
-        <v>1000</v>
+        <v>1732</v>
       </c>
       <c r="Y309">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="Z309">
-        <v>500</v>
+        <v>1332</v>
       </c>
       <c r="AA309">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AB309" t="s">
         <v>41</v>
       </c>
       <c r="AC309" t="s">
-        <v>275</v>
+        <v>1113</v>
       </c>
       <c r="AD309" t="s">
-        <v>1118</v>
+        <v>1117</v>
+      </c>
+      <c r="AE309" t="s">
+        <v>1208</v>
       </c>
       <c r="AF309">
-        <v>620</v>
+        <v>481</v>
       </c>
       <c r="AG309" t="s">
-        <v>103</v>
+        <v>1252</v>
       </c>
       <c r="AH309">
         <v>0</v>
@@ -37612,46 +37717,43 @@
       <c r="AJ309">
         <v>1</v>
       </c>
-      <c r="AK309" t="s">
-        <v>1131</v>
-      </c>
     </row>
     <row r="310" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A310">
-        <v>6006</v>
+        <v>4307</v>
       </c>
       <c r="B310" t="s">
-        <v>1134</v>
+        <v>1254</v>
       </c>
       <c r="C310" t="s">
-        <v>1137</v>
+        <v>1256</v>
       </c>
       <c r="D310">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E310">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F310">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G310">
         <v>100</v>
       </c>
       <c r="H310">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I310">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J310">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="K310">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L310">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M310">
         <v>10</v>
@@ -37660,16 +37762,16 @@
         <v>1</v>
       </c>
       <c r="O310">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="P310">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="Q310">
         <v>105</v>
       </c>
       <c r="R310">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="S310">
         <v>10</v>
@@ -37681,40 +37783,40 @@
         <v>47</v>
       </c>
       <c r="V310" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="W310" t="s">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="X310">
-        <v>916</v>
+        <v>1260</v>
       </c>
       <c r="Y310">
-        <v>576</v>
+        <v>336</v>
       </c>
       <c r="Z310">
-        <v>648</v>
+        <v>960</v>
       </c>
       <c r="AA310">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="AB310" t="s">
         <v>41</v>
       </c>
       <c r="AC310" t="s">
-        <v>48</v>
+        <v>275</v>
       </c>
       <c r="AD310" t="s">
-        <v>1118</v>
+        <v>1194</v>
       </c>
       <c r="AE310" t="s">
-        <v>1182</v>
+        <v>1208</v>
       </c>
       <c r="AF310">
-        <v>180</v>
+        <v>496</v>
       </c>
       <c r="AG310" t="s">
-        <v>1140</v>
+        <v>1255</v>
       </c>
       <c r="AH310">
         <v>0</v>
@@ -37728,16 +37830,16 @@
     </row>
     <row r="311" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A311">
-        <v>6007</v>
-      </c>
-      <c r="B311" s="9" t="s">
-        <v>1135</v>
+        <v>4308</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1257</v>
       </c>
       <c r="C311" t="s">
-        <v>1138</v>
+        <v>1259</v>
       </c>
       <c r="D311">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="E311">
         <v>100</v>
@@ -37746,22 +37848,22 @@
         <v>100</v>
       </c>
       <c r="G311">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H311">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="I311">
+        <v>100</v>
+      </c>
+      <c r="J311">
         <v>130</v>
       </c>
-      <c r="J311">
-        <v>85</v>
-      </c>
       <c r="K311">
         <v>100</v>
       </c>
       <c r="L311">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="M311">
         <v>10</v>
@@ -37770,16 +37872,16 @@
         <v>1</v>
       </c>
       <c r="O311">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="P311">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="Q311">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="R311">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="S311">
         <v>10</v>
@@ -37788,43 +37890,40 @@
         <v>12</v>
       </c>
       <c r="U311" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="V311" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="W311" t="s">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="X311">
-        <v>1200</v>
+        <v>1492</v>
       </c>
       <c r="Y311">
-        <v>576</v>
+        <v>192</v>
       </c>
       <c r="Z311">
-        <v>648</v>
+        <v>1092</v>
       </c>
       <c r="AA311">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AB311" t="s">
         <v>41</v>
       </c>
       <c r="AC311" t="s">
-        <v>48</v>
+        <v>1096</v>
       </c>
       <c r="AD311" t="s">
-        <v>1118</v>
-      </c>
-      <c r="AE311" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="AF311">
-        <v>144</v>
+        <v>870</v>
       </c>
       <c r="AG311" t="s">
-        <v>1141</v>
+        <v>1258</v>
       </c>
       <c r="AH311">
         <v>0</v>
@@ -37838,58 +37937,58 @@
     </row>
     <row r="312" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A312">
-        <v>6008</v>
-      </c>
-      <c r="B312" s="9" t="s">
-        <v>1136</v>
+        <v>4309</v>
+      </c>
+      <c r="B312" t="s">
+        <v>1260</v>
       </c>
       <c r="C312" t="s">
-        <v>1139</v>
+        <v>1262</v>
       </c>
       <c r="D312">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E312">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F312">
         <v>100</v>
       </c>
       <c r="G312">
+        <v>170</v>
+      </c>
+      <c r="H312">
+        <v>100</v>
+      </c>
+      <c r="I312">
+        <v>140</v>
+      </c>
+      <c r="J312">
+        <v>120</v>
+      </c>
+      <c r="K312">
         <v>130</v>
       </c>
-      <c r="H312">
-        <v>100</v>
-      </c>
-      <c r="I312">
-        <v>90</v>
-      </c>
-      <c r="J312">
-        <v>130</v>
-      </c>
-      <c r="K312">
-        <v>110</v>
-      </c>
       <c r="L312">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M312">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="N312">
         <v>1</v>
       </c>
       <c r="O312">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="P312">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="Q312">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="R312">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="S312">
         <v>10</v>
@@ -37898,43 +37997,40 @@
         <v>12</v>
       </c>
       <c r="U312" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="V312" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="W312" t="s">
-        <v>113</v>
+        <v>270</v>
       </c>
       <c r="X312">
-        <v>800</v>
+        <v>1700</v>
       </c>
       <c r="Y312">
-        <v>576</v>
+        <v>500</v>
       </c>
       <c r="Z312">
-        <v>648</v>
+        <v>1000</v>
       </c>
       <c r="AA312">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AB312" t="s">
         <v>41</v>
       </c>
       <c r="AC312" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="AD312" t="s">
-        <v>1118</v>
-      </c>
-      <c r="AE312" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="AF312">
-        <v>144</v>
+        <v>444</v>
       </c>
       <c r="AG312" t="s">
-        <v>1142</v>
+        <v>1261</v>
       </c>
       <c r="AH312">
         <v>0</v>
@@ -37948,16 +38044,16 @@
     </row>
     <row r="313" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A313">
-        <v>6009</v>
+        <v>4310</v>
       </c>
       <c r="B313" t="s">
-        <v>1143</v>
+        <v>1263</v>
       </c>
       <c r="C313" t="s">
-        <v>1146</v>
+        <v>1265</v>
       </c>
       <c r="D313">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="E313">
         <v>100</v>
@@ -37969,19 +38065,19 @@
         <v>100</v>
       </c>
       <c r="H313">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I313">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J313">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="K313">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L313">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="M313">
         <v>10</v>
@@ -37990,16 +38086,16 @@
         <v>1</v>
       </c>
       <c r="O313">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="P313">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="Q313">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="R313">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="S313">
         <v>10</v>
@@ -38008,49 +38104,46 @@
         <v>12</v>
       </c>
       <c r="U313" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="V313" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="W313" t="s">
-        <v>49</v>
+        <v>270</v>
       </c>
       <c r="X313">
-        <v>600</v>
+        <v>2190</v>
       </c>
       <c r="Y313">
-        <v>384</v>
+        <v>336</v>
       </c>
       <c r="Z313">
-        <v>288</v>
+        <v>2040</v>
       </c>
       <c r="AA313">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="AB313" t="s">
         <v>41</v>
       </c>
       <c r="AC313" t="s">
-        <v>48</v>
+        <v>1268</v>
       </c>
       <c r="AD313" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AE313" t="s">
-        <v>1182</v>
+        <v>99</v>
       </c>
       <c r="AF313">
-        <v>180</v>
+        <v>744</v>
       </c>
       <c r="AG313" t="s">
-        <v>1151</v>
+        <v>1264</v>
       </c>
       <c r="AH313">
         <v>0</v>
       </c>
       <c r="AI313">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AJ313">
         <v>1</v>
@@ -38058,40 +38151,40 @@
     </row>
     <row r="314" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A314">
-        <v>6010</v>
+        <v>4311</v>
       </c>
       <c r="B314" t="s">
-        <v>1144</v>
+        <v>1270</v>
       </c>
       <c r="C314" t="s">
-        <v>1147</v>
+        <v>1272</v>
       </c>
       <c r="D314">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="E314">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F314">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G314">
         <v>100</v>
       </c>
       <c r="H314">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="I314">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="J314">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="K314">
         <v>100</v>
       </c>
       <c r="L314">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="M314">
         <v>10</v>
@@ -38100,16 +38193,16 @@
         <v>1</v>
       </c>
       <c r="O314">
-        <v>50</v>
+        <v>270</v>
       </c>
       <c r="P314">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q314">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="R314">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="S314">
         <v>10</v>
@@ -38121,46 +38214,43 @@
         <v>47</v>
       </c>
       <c r="V314" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="W314" t="s">
-        <v>49</v>
+        <v>480</v>
       </c>
       <c r="X314">
-        <v>600</v>
+        <v>1080</v>
       </c>
       <c r="Y314">
-        <v>576</v>
+        <v>180</v>
       </c>
       <c r="Z314">
-        <v>288</v>
+        <v>780</v>
       </c>
       <c r="AA314">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AB314" t="s">
         <v>41</v>
       </c>
       <c r="AC314" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="AD314" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AE314" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="AF314">
-        <v>144</v>
+        <v>900</v>
       </c>
       <c r="AG314" t="s">
-        <v>1152</v>
+        <v>1271</v>
       </c>
       <c r="AH314">
         <v>0</v>
       </c>
       <c r="AI314">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AJ314">
         <v>1</v>
@@ -38168,40 +38258,40 @@
     </row>
     <row r="315" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A315">
-        <v>6011</v>
+        <v>4312</v>
       </c>
       <c r="B315" t="s">
-        <v>1145</v>
+        <v>1273</v>
       </c>
       <c r="C315" t="s">
-        <v>1148</v>
+        <v>1275</v>
       </c>
       <c r="D315">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="E315">
         <v>100</v>
       </c>
       <c r="F315">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G315">
         <v>100</v>
       </c>
       <c r="H315">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I315">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J315">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="K315">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L315">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="M315">
         <v>10</v>
@@ -38210,16 +38300,16 @@
         <v>1</v>
       </c>
       <c r="O315">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="P315">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="Q315">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="R315">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="S315">
         <v>10</v>
@@ -38231,46 +38321,43 @@
         <v>47</v>
       </c>
       <c r="V315" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="W315" t="s">
-        <v>49</v>
+        <v>249</v>
       </c>
       <c r="X315">
-        <v>600</v>
+        <v>1264</v>
       </c>
       <c r="Y315">
         <v>576</v>
       </c>
       <c r="Z315">
-        <v>288</v>
+        <v>864</v>
       </c>
       <c r="AA315">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AB315" t="s">
         <v>41</v>
       </c>
       <c r="AC315" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="AD315" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AE315" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="AF315">
-        <v>144</v>
+        <v>400</v>
       </c>
       <c r="AG315" t="s">
-        <v>1153</v>
+        <v>1274</v>
       </c>
       <c r="AH315">
         <v>0</v>
       </c>
       <c r="AI315">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AJ315">
         <v>1</v>
@@ -38278,58 +38365,58 @@
     </row>
     <row r="316" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A316">
-        <v>6012</v>
+        <v>5000</v>
       </c>
       <c r="B316" t="s">
-        <v>1149</v>
+        <v>44</v>
       </c>
       <c r="C316" t="s">
-        <v>1150</v>
+        <v>37</v>
       </c>
       <c r="D316">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E316">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F316">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G316">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H316">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I316">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J316">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K316">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L316">
         <v>100</v>
       </c>
       <c r="M316">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N316">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O316">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P316">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q316">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="R316">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="S316">
         <v>10</v>
@@ -38338,108 +38425,105 @@
         <v>12</v>
       </c>
       <c r="U316" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="V316" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="W316" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="X316">
-        <v>1001</v>
+        <v>1872</v>
       </c>
       <c r="Y316">
-        <v>1</v>
+        <v>480</v>
       </c>
       <c r="Z316">
-        <v>1</v>
+        <v>672</v>
       </c>
       <c r="AA316">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB316" t="s">
         <v>41</v>
       </c>
       <c r="AC316" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="AD316" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE316" t="s">
-        <v>1182</v>
+        <v>1115</v>
       </c>
       <c r="AF316">
-        <v>672</v>
+        <v>288</v>
       </c>
       <c r="AG316" t="s">
-        <v>334</v>
+        <v>43</v>
       </c>
       <c r="AH316">
         <v>0</v>
       </c>
       <c r="AI316">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AJ316">
-        <v>1.05</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="317" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A317">
-        <v>6013</v>
+        <v>6000</v>
       </c>
       <c r="B317" t="s">
-        <v>1156</v>
+        <v>1091</v>
       </c>
       <c r="C317" t="s">
-        <v>1158</v>
+        <v>565</v>
       </c>
       <c r="D317">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="E317">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="F317">
         <v>100</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H317">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I317">
         <v>120</v>
       </c>
       <c r="J317">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K317">
+        <v>200</v>
+      </c>
+      <c r="L317">
+        <v>75</v>
+      </c>
+      <c r="M317">
+        <v>15</v>
+      </c>
+      <c r="N317">
+        <v>1</v>
+      </c>
+      <c r="O317">
+        <v>40</v>
+      </c>
+      <c r="P317">
+        <v>130</v>
+      </c>
+      <c r="Q317">
         <v>0</v>
       </c>
-      <c r="L317">
-        <v>130</v>
-      </c>
-      <c r="M317">
-        <v>10</v>
-      </c>
-      <c r="N317">
-        <v>1</v>
-      </c>
-      <c r="O317">
+      <c r="R317">
         <v>0</v>
-      </c>
-      <c r="P317">
-        <v>0</v>
-      </c>
-      <c r="Q317">
-        <v>110</v>
-      </c>
-      <c r="R317">
-        <v>80</v>
       </c>
       <c r="S317">
         <v>10</v>
@@ -38451,40 +38535,37 @@
         <v>38</v>
       </c>
       <c r="V317" t="s">
-        <v>39</v>
+        <v>219</v>
       </c>
       <c r="W317" t="s">
-        <v>437</v>
+        <v>274</v>
       </c>
       <c r="X317">
-        <v>1472</v>
+        <v>1276</v>
       </c>
       <c r="Y317">
         <v>288</v>
       </c>
       <c r="Z317">
-        <v>672</v>
+        <v>576</v>
       </c>
       <c r="AA317">
+        <v>150</v>
+      </c>
+      <c r="AB317" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC317" t="s">
+        <v>566</v>
+      </c>
+      <c r="AD317" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AF317">
         <v>180</v>
       </c>
-      <c r="AB317" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC317" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD317" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE317" t="s">
-        <v>1158</v>
-      </c>
-      <c r="AF317">
-        <v>528</v>
-      </c>
       <c r="AG317" t="s">
-        <v>1154</v>
+        <v>567</v>
       </c>
       <c r="AH317">
         <v>0</v>
@@ -38495,174 +38576,174 @@
       <c r="AJ317">
         <v>1</v>
       </c>
+      <c r="AK317" t="s">
+        <v>1092</v>
+      </c>
     </row>
     <row r="318" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A318">
-        <v>6014</v>
+        <v>6001</v>
       </c>
       <c r="B318" t="s">
-        <v>1157</v>
+        <v>1100</v>
       </c>
       <c r="C318" t="s">
-        <v>1159</v>
+        <v>77</v>
       </c>
       <c r="D318">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E318">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F318">
         <v>100</v>
       </c>
       <c r="G318">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H318">
         <v>80</v>
       </c>
       <c r="I318">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J318">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="K318">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L318">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M318">
         <v>10</v>
       </c>
       <c r="N318">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O318">
+        <v>100</v>
+      </c>
+      <c r="P318">
+        <v>100</v>
+      </c>
+      <c r="Q318">
         <v>0</v>
       </c>
-      <c r="P318">
+      <c r="R318">
         <v>0</v>
       </c>
-      <c r="Q318">
-        <v>125</v>
-      </c>
-      <c r="R318">
-        <v>80</v>
-      </c>
       <c r="S318">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T318">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="U318" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="V318" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="W318" t="s">
-        <v>1025</v>
+        <v>619</v>
       </c>
       <c r="X318">
-        <v>1272</v>
+        <v>701</v>
       </c>
       <c r="Y318">
+        <v>1</v>
+      </c>
+      <c r="Z318">
+        <v>1</v>
+      </c>
+      <c r="AA318">
+        <v>-1</v>
+      </c>
+      <c r="AB318" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC318" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AD318" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF318">
         <v>288</v>
       </c>
-      <c r="Z318">
-        <v>672</v>
-      </c>
-      <c r="AA318">
-        <v>170</v>
-      </c>
-      <c r="AB318" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC318" t="s">
-        <v>225</v>
-      </c>
-      <c r="AD318" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE318" t="s">
-        <v>1158</v>
-      </c>
-      <c r="AF318">
-        <v>528</v>
-      </c>
       <c r="AG318" t="s">
-        <v>1155</v>
+        <v>79</v>
       </c>
       <c r="AH318">
         <v>0</v>
       </c>
       <c r="AI318">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="AJ318">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="319" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A319">
-        <v>6015</v>
+        <v>6002</v>
       </c>
       <c r="B319" t="s">
-        <v>1206</v>
+        <v>1101</v>
       </c>
       <c r="C319" t="s">
-        <v>1207</v>
+        <v>1102</v>
       </c>
       <c r="D319">
+        <v>24</v>
+      </c>
+      <c r="E319">
+        <v>90</v>
+      </c>
+      <c r="F319">
+        <v>100</v>
+      </c>
+      <c r="G319">
+        <v>100</v>
+      </c>
+      <c r="H319">
+        <v>100</v>
+      </c>
+      <c r="I319">
+        <v>100</v>
+      </c>
+      <c r="J319">
+        <v>100</v>
+      </c>
+      <c r="K319">
+        <v>100</v>
+      </c>
+      <c r="L319">
+        <v>105</v>
+      </c>
+      <c r="M319">
         <v>10</v>
       </c>
-      <c r="E319">
-        <v>80</v>
-      </c>
-      <c r="F319">
-        <v>80</v>
-      </c>
-      <c r="G319">
-        <v>80</v>
-      </c>
-      <c r="H319">
-        <v>80</v>
-      </c>
-      <c r="I319">
-        <v>80</v>
-      </c>
-      <c r="J319">
-        <v>80</v>
-      </c>
-      <c r="K319">
-        <v>80</v>
-      </c>
-      <c r="L319">
-        <v>100</v>
-      </c>
-      <c r="M319">
-        <v>5</v>
-      </c>
       <c r="N319">
         <v>1</v>
       </c>
       <c r="O319">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P319">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q319">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R319">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S319">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T319">
         <v>12</v>
@@ -38671,37 +38752,37 @@
         <v>38</v>
       </c>
       <c r="V319" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="W319" t="s">
-        <v>109</v>
+        <v>619</v>
       </c>
       <c r="X319">
-        <v>1872</v>
+        <v>500</v>
       </c>
       <c r="Y319">
-        <v>480</v>
+        <v>288</v>
       </c>
       <c r="Z319">
-        <v>672</v>
+        <v>288</v>
       </c>
       <c r="AA319">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="AB319" t="s">
         <v>41</v>
       </c>
       <c r="AC319" t="s">
-        <v>39</v>
+        <v>1086</v>
       </c>
       <c r="AD319" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="AF319">
-        <v>288</v>
+        <v>504</v>
       </c>
       <c r="AG319" t="s">
-        <v>1208</v>
+        <v>283</v>
       </c>
       <c r="AH319">
         <v>0</v>
@@ -38710,36 +38791,39 @@
         <v>0.5</v>
       </c>
       <c r="AJ319">
-        <v>1</v>
+        <v>0.7</v>
+      </c>
+      <c r="AK319" t="s">
+        <v>1103</v>
       </c>
     </row>
     <row r="320" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A320">
-        <v>6016</v>
+        <v>6003</v>
       </c>
       <c r="B320" t="s">
-        <v>1212</v>
+        <v>1120</v>
       </c>
       <c r="C320" t="s">
-        <v>1224</v>
+        <v>1121</v>
       </c>
       <c r="D320">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="E320">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="F320">
         <v>100</v>
       </c>
       <c r="G320">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H320">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I320">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="J320">
         <v>100</v>
@@ -38748,19 +38832,19 @@
         <v>100</v>
       </c>
       <c r="L320">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="M320">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N320">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O320">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P320">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="Q320">
         <v>100</v>
@@ -38778,37 +38862,40 @@
         <v>38</v>
       </c>
       <c r="V320" t="s">
-        <v>219</v>
+        <v>53</v>
       </c>
       <c r="W320" t="s">
-        <v>619</v>
+        <v>49</v>
       </c>
       <c r="X320">
-        <v>1306</v>
+        <v>902</v>
       </c>
       <c r="Y320">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="Z320">
-        <v>1056</v>
+        <v>648</v>
       </c>
       <c r="AA320">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="AB320" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="AC320" t="s">
-        <v>1114</v>
+        <v>120</v>
       </c>
       <c r="AD320" t="s">
-        <v>1119</v>
+        <v>1118</v>
+      </c>
+      <c r="AE320" t="s">
+        <v>1203</v>
       </c>
       <c r="AF320">
-        <v>576</v>
+        <v>216</v>
       </c>
       <c r="AG320" t="s">
-        <v>1213</v>
+        <v>1122</v>
       </c>
       <c r="AH320">
         <v>0</v>
@@ -38820,18 +38907,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A321">
-        <v>6017</v>
+        <v>6004</v>
       </c>
       <c r="B321" t="s">
-        <v>1214</v>
+        <v>1123</v>
       </c>
       <c r="C321" t="s">
-        <v>1225</v>
+        <v>1124</v>
       </c>
       <c r="D321">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E321">
         <v>100</v>
@@ -38840,13 +38927,13 @@
         <v>100</v>
       </c>
       <c r="G321">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H321">
         <v>100</v>
       </c>
       <c r="I321">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="J321">
         <v>100</v>
@@ -38861,13 +38948,13 @@
         <v>10</v>
       </c>
       <c r="N321">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O321">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="P321">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Q321">
         <v>100</v>
@@ -38885,37 +38972,37 @@
         <v>38</v>
       </c>
       <c r="V321" t="s">
-        <v>219</v>
+        <v>53</v>
       </c>
       <c r="W321" t="s">
-        <v>619</v>
+        <v>40</v>
       </c>
       <c r="X321">
-        <v>850</v>
+        <v>1540</v>
       </c>
       <c r="Y321">
-        <v>336</v>
+        <v>576</v>
       </c>
       <c r="Z321">
-        <v>600</v>
+        <v>720</v>
       </c>
       <c r="AA321">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="AB321" t="s">
         <v>41</v>
       </c>
       <c r="AC321" t="s">
-        <v>1114</v>
+        <v>41</v>
       </c>
       <c r="AD321" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="AF321">
-        <v>420</v>
+        <v>324</v>
       </c>
       <c r="AG321" t="s">
-        <v>1215</v>
+        <v>1125</v>
       </c>
       <c r="AH321">
         <v>0</v>
@@ -38927,18 +39014,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A322">
-        <v>6018</v>
+        <v>6005</v>
       </c>
       <c r="B322" t="s">
-        <v>1216</v>
+        <v>1131</v>
       </c>
       <c r="C322" t="s">
-        <v>1230</v>
+        <v>1132</v>
       </c>
       <c r="D322">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="E322">
         <v>100</v>
@@ -38953,13 +39040,13 @@
         <v>100</v>
       </c>
       <c r="I322">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J322">
         <v>100</v>
       </c>
       <c r="K322">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L322">
         <v>100</v>
@@ -38968,13 +39055,13 @@
         <v>10</v>
       </c>
       <c r="N322">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O322">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P322">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q322">
         <v>100</v>
@@ -38989,40 +39076,40 @@
         <v>12</v>
       </c>
       <c r="U322" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="V322" t="s">
-        <v>229</v>
+        <v>53</v>
       </c>
       <c r="W322" t="s">
-        <v>585</v>
+        <v>49</v>
       </c>
       <c r="X322">
-        <v>432</v>
+        <v>1000</v>
       </c>
       <c r="Y322">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="Z322">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="AA322">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AB322" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="AC322" t="s">
-        <v>1227</v>
+        <v>275</v>
       </c>
       <c r="AD322" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="AF322">
-        <v>300</v>
+        <v>620</v>
       </c>
       <c r="AG322" t="s">
-        <v>1217</v>
+        <v>103</v>
       </c>
       <c r="AH322">
         <v>0</v>
@@ -39033,22 +39120,25 @@
       <c r="AJ322">
         <v>1</v>
       </c>
-    </row>
-    <row r="323" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="AK322" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="323" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A323">
-        <v>6019</v>
+        <v>6006</v>
       </c>
       <c r="B323" t="s">
-        <v>1218</v>
+        <v>1133</v>
       </c>
       <c r="C323" t="s">
-        <v>1229</v>
+        <v>1136</v>
       </c>
       <c r="D323">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E323">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F323">
         <v>100</v>
@@ -39057,7 +39147,7 @@
         <v>100</v>
       </c>
       <c r="H323">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="I323">
         <v>100</v>
@@ -39066,7 +39156,7 @@
         <v>100</v>
       </c>
       <c r="K323">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L323">
         <v>100</v>
@@ -39075,16 +39165,16 @@
         <v>10</v>
       </c>
       <c r="N323">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O323">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="P323">
         <v>100</v>
       </c>
       <c r="Q323">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="R323">
         <v>100</v>
@@ -39096,40 +39186,43 @@
         <v>12</v>
       </c>
       <c r="U323" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="V323" t="s">
-        <v>229</v>
+        <v>48</v>
       </c>
       <c r="W323" t="s">
-        <v>619</v>
+        <v>113</v>
       </c>
       <c r="X323">
-        <v>360</v>
+        <v>916</v>
       </c>
       <c r="Y323">
-        <v>360</v>
+        <v>576</v>
       </c>
       <c r="Z323">
-        <v>480</v>
+        <v>648</v>
       </c>
       <c r="AA323">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AB323" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="AC323" t="s">
-        <v>1227</v>
+        <v>48</v>
       </c>
       <c r="AD323" t="s">
-        <v>1119</v>
+        <v>1117</v>
+      </c>
+      <c r="AE323" t="s">
+        <v>1181</v>
       </c>
       <c r="AF323">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AG323" t="s">
-        <v>1219</v>
+        <v>1139</v>
       </c>
       <c r="AH323">
         <v>0</v>
@@ -39141,18 +39234,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A324">
-        <v>6020</v>
-      </c>
-      <c r="B324" t="s">
-        <v>1220</v>
+        <v>6007</v>
+      </c>
+      <c r="B324" s="9" t="s">
+        <v>1134</v>
       </c>
       <c r="C324" t="s">
-        <v>1230</v>
+        <v>1137</v>
       </c>
       <c r="D324">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="E324">
         <v>100</v>
@@ -39167,22 +39260,22 @@
         <v>100</v>
       </c>
       <c r="I324">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="J324">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K324">
         <v>100</v>
       </c>
       <c r="L324">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M324">
         <v>10</v>
       </c>
       <c r="N324">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O324">
         <v>100</v>
@@ -39191,10 +39284,10 @@
         <v>100</v>
       </c>
       <c r="Q324">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="R324">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="S324">
         <v>10</v>
@@ -39203,40 +39296,43 @@
         <v>12</v>
       </c>
       <c r="U324" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="V324" t="s">
-        <v>229</v>
+        <v>48</v>
       </c>
       <c r="W324" t="s">
-        <v>865</v>
+        <v>113</v>
       </c>
       <c r="X324">
+        <v>1200</v>
+      </c>
+      <c r="Y324">
         <v>576</v>
       </c>
-      <c r="Y324">
-        <v>360</v>
-      </c>
       <c r="Z324">
-        <v>420</v>
+        <v>648</v>
       </c>
       <c r="AA324">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB324" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="AC324" t="s">
-        <v>1226</v>
+        <v>48</v>
       </c>
       <c r="AD324" t="s">
-        <v>1119</v>
+        <v>1117</v>
+      </c>
+      <c r="AE324" t="s">
+        <v>1181</v>
       </c>
       <c r="AF324">
-        <v>384</v>
+        <v>144</v>
       </c>
       <c r="AG324" t="s">
-        <v>1221</v>
+        <v>1140</v>
       </c>
       <c r="AH324">
         <v>0</v>
@@ -39248,39 +39344,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A325">
-        <v>6021</v>
-      </c>
-      <c r="B325" t="s">
-        <v>1222</v>
+        <v>6008</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>1135</v>
       </c>
       <c r="C325" t="s">
-        <v>1231</v>
+        <v>1138</v>
       </c>
       <c r="D325">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="E325">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F325">
         <v>100</v>
       </c>
       <c r="G325">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H325">
         <v>100</v>
       </c>
       <c r="I325">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J325">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="K325">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L325">
         <v>100</v>
@@ -39289,19 +39385,19 @@
         <v>10</v>
       </c>
       <c r="N325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O325">
         <v>100</v>
       </c>
       <c r="P325">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="Q325">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="R325">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="S325">
         <v>10</v>
@@ -39310,40 +39406,43 @@
         <v>12</v>
       </c>
       <c r="U325" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="V325" t="s">
-        <v>229</v>
+        <v>48</v>
       </c>
       <c r="W325" t="s">
-        <v>865</v>
+        <v>113</v>
       </c>
       <c r="X325">
-        <v>432</v>
+        <v>800</v>
       </c>
       <c r="Y325">
-        <v>360</v>
+        <v>576</v>
       </c>
       <c r="Z325">
-        <v>420</v>
+        <v>648</v>
       </c>
       <c r="AA325">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AB325" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="AC325" t="s">
-        <v>1228</v>
+        <v>48</v>
       </c>
       <c r="AD325" t="s">
-        <v>1119</v>
+        <v>1117</v>
+      </c>
+      <c r="AE325" t="s">
+        <v>1181</v>
       </c>
       <c r="AF325">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="AG325" t="s">
-        <v>1223</v>
+        <v>1141</v>
       </c>
       <c r="AH325">
         <v>0</v>
@@ -39355,60 +39454,60 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A326">
-        <v>6022</v>
+        <v>6009</v>
       </c>
       <c r="B326" t="s">
-        <v>1236</v>
+        <v>1142</v>
       </c>
       <c r="C326" t="s">
-        <v>1237</v>
+        <v>1145</v>
       </c>
       <c r="D326">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="E326">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F326">
         <v>100</v>
       </c>
       <c r="G326">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H326">
         <v>30</v>
       </c>
       <c r="I326">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="J326">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K326">
         <v>100</v>
       </c>
       <c r="L326">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="M326">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N326">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O326">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="P326">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Q326">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="R326">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="S326">
         <v>10</v>
@@ -39417,22 +39516,22 @@
         <v>12</v>
       </c>
       <c r="U326" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="V326" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="W326" t="s">
-        <v>532</v>
+        <v>49</v>
       </c>
       <c r="X326">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="Y326">
-        <v>750</v>
+        <v>384</v>
       </c>
       <c r="Z326">
-        <v>1000</v>
+        <v>288</v>
       </c>
       <c r="AA326">
         <v>160</v>
@@ -39441,24 +39540,1219 @@
         <v>41</v>
       </c>
       <c r="AC326" t="s">
-        <v>1112</v>
+        <v>48</v>
       </c>
       <c r="AD326" t="s">
-        <v>99</v>
+        <v>1116</v>
+      </c>
+      <c r="AE326" t="s">
+        <v>1181</v>
       </c>
       <c r="AF326">
-        <v>972</v>
+        <v>180</v>
       </c>
       <c r="AG326" t="s">
-        <v>1238</v>
+        <v>1150</v>
       </c>
       <c r="AH326">
         <v>0</v>
       </c>
       <c r="AI326">
+        <v>0.25</v>
+      </c>
+      <c r="AJ326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A327">
+        <v>6010</v>
+      </c>
+      <c r="B327" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C327" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D327">
+        <v>20</v>
+      </c>
+      <c r="E327">
+        <v>100</v>
+      </c>
+      <c r="F327">
+        <v>100</v>
+      </c>
+      <c r="G327">
+        <v>100</v>
+      </c>
+      <c r="H327">
+        <v>30</v>
+      </c>
+      <c r="I327">
+        <v>140</v>
+      </c>
+      <c r="J327">
+        <v>140</v>
+      </c>
+      <c r="K327">
+        <v>100</v>
+      </c>
+      <c r="L327">
+        <v>160</v>
+      </c>
+      <c r="M327">
+        <v>10</v>
+      </c>
+      <c r="N327">
+        <v>1</v>
+      </c>
+      <c r="O327">
+        <v>50</v>
+      </c>
+      <c r="P327">
+        <v>50</v>
+      </c>
+      <c r="Q327">
+        <v>170</v>
+      </c>
+      <c r="R327">
+        <v>170</v>
+      </c>
+      <c r="S327">
+        <v>10</v>
+      </c>
+      <c r="T327">
+        <v>12</v>
+      </c>
+      <c r="U327" t="s">
+        <v>47</v>
+      </c>
+      <c r="V327" t="s">
+        <v>48</v>
+      </c>
+      <c r="W327" t="s">
+        <v>49</v>
+      </c>
+      <c r="X327">
+        <v>600</v>
+      </c>
+      <c r="Y327">
+        <v>576</v>
+      </c>
+      <c r="Z327">
+        <v>288</v>
+      </c>
+      <c r="AA327">
+        <v>80</v>
+      </c>
+      <c r="AB327" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC327" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD327" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AE327" t="s">
+        <v>1181</v>
+      </c>
+      <c r="AF327">
+        <v>144</v>
+      </c>
+      <c r="AG327" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AH327">
+        <v>0</v>
+      </c>
+      <c r="AI327">
+        <v>0.25</v>
+      </c>
+      <c r="AJ327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A328">
+        <v>6011</v>
+      </c>
+      <c r="B328" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C328" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D328">
+        <v>22</v>
+      </c>
+      <c r="E328">
+        <v>100</v>
+      </c>
+      <c r="F328">
+        <v>100</v>
+      </c>
+      <c r="G328">
+        <v>100</v>
+      </c>
+      <c r="H328">
+        <v>30</v>
+      </c>
+      <c r="I328">
+        <v>100</v>
+      </c>
+      <c r="J328">
+        <v>140</v>
+      </c>
+      <c r="K328">
+        <v>100</v>
+      </c>
+      <c r="L328">
+        <v>160</v>
+      </c>
+      <c r="M328">
+        <v>10</v>
+      </c>
+      <c r="N328">
+        <v>1</v>
+      </c>
+      <c r="O328">
+        <v>50</v>
+      </c>
+      <c r="P328">
+        <v>50</v>
+      </c>
+      <c r="Q328">
+        <v>170</v>
+      </c>
+      <c r="R328">
+        <v>170</v>
+      </c>
+      <c r="S328">
+        <v>10</v>
+      </c>
+      <c r="T328">
+        <v>12</v>
+      </c>
+      <c r="U328" t="s">
+        <v>47</v>
+      </c>
+      <c r="V328" t="s">
+        <v>48</v>
+      </c>
+      <c r="W328" t="s">
+        <v>49</v>
+      </c>
+      <c r="X328">
+        <v>600</v>
+      </c>
+      <c r="Y328">
+        <v>576</v>
+      </c>
+      <c r="Z328">
+        <v>288</v>
+      </c>
+      <c r="AA328">
+        <v>140</v>
+      </c>
+      <c r="AB328" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC328" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD328" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AE328" t="s">
+        <v>1181</v>
+      </c>
+      <c r="AF328">
+        <v>144</v>
+      </c>
+      <c r="AG328" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AH328">
+        <v>0</v>
+      </c>
+      <c r="AI328">
+        <v>0.25</v>
+      </c>
+      <c r="AJ328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A329">
+        <v>6012</v>
+      </c>
+      <c r="B329" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C329" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D329">
+        <v>20</v>
+      </c>
+      <c r="E329">
+        <v>100</v>
+      </c>
+      <c r="F329">
+        <v>100</v>
+      </c>
+      <c r="G329">
+        <v>100</v>
+      </c>
+      <c r="H329">
+        <v>100</v>
+      </c>
+      <c r="I329">
+        <v>100</v>
+      </c>
+      <c r="J329">
+        <v>100</v>
+      </c>
+      <c r="K329">
+        <v>100</v>
+      </c>
+      <c r="L329">
+        <v>100</v>
+      </c>
+      <c r="M329">
+        <v>10</v>
+      </c>
+      <c r="N329">
+        <v>0</v>
+      </c>
+      <c r="O329">
+        <v>100</v>
+      </c>
+      <c r="P329">
+        <v>100</v>
+      </c>
+      <c r="Q329">
+        <v>170</v>
+      </c>
+      <c r="R329">
+        <v>170</v>
+      </c>
+      <c r="S329">
+        <v>10</v>
+      </c>
+      <c r="T329">
+        <v>12</v>
+      </c>
+      <c r="U329" t="s">
+        <v>47</v>
+      </c>
+      <c r="V329" t="s">
+        <v>140</v>
+      </c>
+      <c r="W329" t="s">
+        <v>54</v>
+      </c>
+      <c r="X329">
+        <v>1001</v>
+      </c>
+      <c r="Y329">
+        <v>1</v>
+      </c>
+      <c r="Z329">
+        <v>1</v>
+      </c>
+      <c r="AA329">
+        <v>1000</v>
+      </c>
+      <c r="AB329" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC329" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD329" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE329" t="s">
+        <v>1181</v>
+      </c>
+      <c r="AF329">
+        <v>672</v>
+      </c>
+      <c r="AG329" t="s">
+        <v>334</v>
+      </c>
+      <c r="AH329">
+        <v>0</v>
+      </c>
+      <c r="AI329">
+        <v>-1</v>
+      </c>
+      <c r="AJ329">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="330" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A330">
+        <v>6013</v>
+      </c>
+      <c r="B330" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C330" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D330">
+        <v>36</v>
+      </c>
+      <c r="E330">
+        <v>90</v>
+      </c>
+      <c r="F330">
+        <v>100</v>
+      </c>
+      <c r="G330">
+        <v>0</v>
+      </c>
+      <c r="H330">
+        <v>80</v>
+      </c>
+      <c r="I330">
+        <v>120</v>
+      </c>
+      <c r="J330">
+        <v>115</v>
+      </c>
+      <c r="K330">
+        <v>0</v>
+      </c>
+      <c r="L330">
+        <v>130</v>
+      </c>
+      <c r="M330">
+        <v>10</v>
+      </c>
+      <c r="N330">
+        <v>1</v>
+      </c>
+      <c r="O330">
+        <v>0</v>
+      </c>
+      <c r="P330">
+        <v>0</v>
+      </c>
+      <c r="Q330">
+        <v>110</v>
+      </c>
+      <c r="R330">
+        <v>80</v>
+      </c>
+      <c r="S330">
+        <v>10</v>
+      </c>
+      <c r="T330">
+        <v>12</v>
+      </c>
+      <c r="U330" t="s">
+        <v>38</v>
+      </c>
+      <c r="V330" t="s">
+        <v>39</v>
+      </c>
+      <c r="W330" t="s">
+        <v>437</v>
+      </c>
+      <c r="X330">
+        <v>1472</v>
+      </c>
+      <c r="Y330">
+        <v>288</v>
+      </c>
+      <c r="Z330">
+        <v>672</v>
+      </c>
+      <c r="AA330">
+        <v>180</v>
+      </c>
+      <c r="AB330" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC330" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD330" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE330" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AF330">
+        <v>528</v>
+      </c>
+      <c r="AG330" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AH330">
+        <v>0</v>
+      </c>
+      <c r="AI330">
         <v>0.5</v>
       </c>
-      <c r="AJ326">
+      <c r="AJ330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A331">
+        <v>6014</v>
+      </c>
+      <c r="B331" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C331" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331">
+        <v>90</v>
+      </c>
+      <c r="F331">
+        <v>100</v>
+      </c>
+      <c r="G331">
+        <v>0</v>
+      </c>
+      <c r="H331">
+        <v>80</v>
+      </c>
+      <c r="I331">
+        <v>120</v>
+      </c>
+      <c r="J331">
+        <v>115</v>
+      </c>
+      <c r="K331">
+        <v>0</v>
+      </c>
+      <c r="L331">
+        <v>200</v>
+      </c>
+      <c r="M331">
+        <v>10</v>
+      </c>
+      <c r="N331">
+        <v>1</v>
+      </c>
+      <c r="O331">
+        <v>0</v>
+      </c>
+      <c r="P331">
+        <v>0</v>
+      </c>
+      <c r="Q331">
+        <v>125</v>
+      </c>
+      <c r="R331">
+        <v>80</v>
+      </c>
+      <c r="S331">
+        <v>10</v>
+      </c>
+      <c r="T331">
+        <v>12</v>
+      </c>
+      <c r="U331" t="s">
+        <v>38</v>
+      </c>
+      <c r="V331" t="s">
+        <v>39</v>
+      </c>
+      <c r="W331" t="s">
+        <v>1024</v>
+      </c>
+      <c r="X331">
+        <v>1272</v>
+      </c>
+      <c r="Y331">
+        <v>288</v>
+      </c>
+      <c r="Z331">
+        <v>672</v>
+      </c>
+      <c r="AA331">
+        <v>170</v>
+      </c>
+      <c r="AB331" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC331" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD331" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE331" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AF331">
+        <v>528</v>
+      </c>
+      <c r="AG331" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AH331">
+        <v>0</v>
+      </c>
+      <c r="AI331">
+        <v>0.5</v>
+      </c>
+      <c r="AJ331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A332">
+        <v>6015</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D332">
+        <v>10</v>
+      </c>
+      <c r="E332">
+        <v>80</v>
+      </c>
+      <c r="F332">
+        <v>80</v>
+      </c>
+      <c r="G332">
+        <v>80</v>
+      </c>
+      <c r="H332">
+        <v>80</v>
+      </c>
+      <c r="I332">
+        <v>80</v>
+      </c>
+      <c r="J332">
+        <v>80</v>
+      </c>
+      <c r="K332">
+        <v>80</v>
+      </c>
+      <c r="L332">
+        <v>100</v>
+      </c>
+      <c r="M332">
+        <v>5</v>
+      </c>
+      <c r="N332">
+        <v>1</v>
+      </c>
+      <c r="O332">
+        <v>50</v>
+      </c>
+      <c r="P332">
+        <v>50</v>
+      </c>
+      <c r="Q332">
+        <v>100</v>
+      </c>
+      <c r="R332">
+        <v>80</v>
+      </c>
+      <c r="S332">
+        <v>10</v>
+      </c>
+      <c r="T332">
+        <v>12</v>
+      </c>
+      <c r="U332" t="s">
+        <v>38</v>
+      </c>
+      <c r="V332" t="s">
+        <v>39</v>
+      </c>
+      <c r="W332" t="s">
+        <v>109</v>
+      </c>
+      <c r="X332">
+        <v>1872</v>
+      </c>
+      <c r="Y332">
+        <v>480</v>
+      </c>
+      <c r="Z332">
+        <v>672</v>
+      </c>
+      <c r="AA332">
+        <v>400</v>
+      </c>
+      <c r="AB332" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC332" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD332" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AF332">
+        <v>288</v>
+      </c>
+      <c r="AG332" t="s">
+        <v>1207</v>
+      </c>
+      <c r="AH332">
+        <v>0</v>
+      </c>
+      <c r="AI332">
+        <v>0.5</v>
+      </c>
+      <c r="AJ332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A333">
+        <v>6018</v>
+      </c>
+      <c r="B333" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C333" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D333">
+        <v>81</v>
+      </c>
+      <c r="E333">
+        <v>100</v>
+      </c>
+      <c r="F333">
+        <v>100</v>
+      </c>
+      <c r="G333">
+        <v>100</v>
+      </c>
+      <c r="H333">
+        <v>100</v>
+      </c>
+      <c r="I333">
+        <v>100</v>
+      </c>
+      <c r="J333">
+        <v>100</v>
+      </c>
+      <c r="K333">
+        <v>100</v>
+      </c>
+      <c r="L333">
+        <v>100</v>
+      </c>
+      <c r="M333">
+        <v>10</v>
+      </c>
+      <c r="N333">
+        <v>2</v>
+      </c>
+      <c r="O333">
+        <v>100</v>
+      </c>
+      <c r="P333">
+        <v>100</v>
+      </c>
+      <c r="Q333">
+        <v>100</v>
+      </c>
+      <c r="R333">
+        <v>100</v>
+      </c>
+      <c r="S333">
+        <v>10</v>
+      </c>
+      <c r="T333">
+        <v>12</v>
+      </c>
+      <c r="U333" t="s">
+        <v>38</v>
+      </c>
+      <c r="V333" t="s">
+        <v>229</v>
+      </c>
+      <c r="W333" t="s">
+        <v>585</v>
+      </c>
+      <c r="X333">
+        <v>432</v>
+      </c>
+      <c r="Y333">
+        <v>360</v>
+      </c>
+      <c r="Z333">
+        <v>480</v>
+      </c>
+      <c r="AA333">
+        <v>100</v>
+      </c>
+      <c r="AB333" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC333" t="s">
+        <v>1226</v>
+      </c>
+      <c r="AD333" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AF333">
+        <v>300</v>
+      </c>
+      <c r="AG333" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AH333">
+        <v>0</v>
+      </c>
+      <c r="AI333">
+        <v>0.5</v>
+      </c>
+      <c r="AJ333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A334">
+        <v>6019</v>
+      </c>
+      <c r="B334" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C334" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D334">
+        <v>79</v>
+      </c>
+      <c r="E334">
+        <v>100</v>
+      </c>
+      <c r="F334">
+        <v>100</v>
+      </c>
+      <c r="G334">
+        <v>100</v>
+      </c>
+      <c r="H334">
+        <v>100</v>
+      </c>
+      <c r="I334">
+        <v>100</v>
+      </c>
+      <c r="J334">
+        <v>100</v>
+      </c>
+      <c r="K334">
+        <v>100</v>
+      </c>
+      <c r="L334">
+        <v>100</v>
+      </c>
+      <c r="M334">
+        <v>10</v>
+      </c>
+      <c r="N334">
+        <v>2</v>
+      </c>
+      <c r="O334">
+        <v>100</v>
+      </c>
+      <c r="P334">
+        <v>100</v>
+      </c>
+      <c r="Q334">
+        <v>100</v>
+      </c>
+      <c r="R334">
+        <v>100</v>
+      </c>
+      <c r="S334">
+        <v>10</v>
+      </c>
+      <c r="T334">
+        <v>12</v>
+      </c>
+      <c r="U334" t="s">
+        <v>38</v>
+      </c>
+      <c r="V334" t="s">
+        <v>229</v>
+      </c>
+      <c r="W334" t="s">
+        <v>619</v>
+      </c>
+      <c r="X334">
+        <v>360</v>
+      </c>
+      <c r="Y334">
+        <v>360</v>
+      </c>
+      <c r="Z334">
+        <v>480</v>
+      </c>
+      <c r="AA334">
+        <v>120</v>
+      </c>
+      <c r="AB334" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC334" t="s">
+        <v>1226</v>
+      </c>
+      <c r="AD334" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AF334">
+        <v>240</v>
+      </c>
+      <c r="AG334" t="s">
+        <v>1218</v>
+      </c>
+      <c r="AH334">
+        <v>0</v>
+      </c>
+      <c r="AI334">
+        <v>0.5</v>
+      </c>
+      <c r="AJ334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A335">
+        <v>6020</v>
+      </c>
+      <c r="B335" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C335" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D335">
+        <v>77</v>
+      </c>
+      <c r="E335">
+        <v>100</v>
+      </c>
+      <c r="F335">
+        <v>100</v>
+      </c>
+      <c r="G335">
+        <v>100</v>
+      </c>
+      <c r="H335">
+        <v>100</v>
+      </c>
+      <c r="I335">
+        <v>100</v>
+      </c>
+      <c r="J335">
+        <v>100</v>
+      </c>
+      <c r="K335">
+        <v>100</v>
+      </c>
+      <c r="L335">
+        <v>100</v>
+      </c>
+      <c r="M335">
+        <v>10</v>
+      </c>
+      <c r="N335">
+        <v>2</v>
+      </c>
+      <c r="O335">
+        <v>100</v>
+      </c>
+      <c r="P335">
+        <v>100</v>
+      </c>
+      <c r="Q335">
+        <v>100</v>
+      </c>
+      <c r="R335">
+        <v>100</v>
+      </c>
+      <c r="S335">
+        <v>10</v>
+      </c>
+      <c r="T335">
+        <v>12</v>
+      </c>
+      <c r="U335" t="s">
+        <v>38</v>
+      </c>
+      <c r="V335" t="s">
+        <v>229</v>
+      </c>
+      <c r="W335" t="s">
+        <v>864</v>
+      </c>
+      <c r="X335">
+        <v>576</v>
+      </c>
+      <c r="Y335">
+        <v>360</v>
+      </c>
+      <c r="Z335">
+        <v>420</v>
+      </c>
+      <c r="AA335">
+        <v>180</v>
+      </c>
+      <c r="AB335" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC335" t="s">
+        <v>1225</v>
+      </c>
+      <c r="AD335" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AF335">
+        <v>384</v>
+      </c>
+      <c r="AG335" t="s">
+        <v>1220</v>
+      </c>
+      <c r="AH335">
+        <v>0</v>
+      </c>
+      <c r="AI335">
+        <v>0.5</v>
+      </c>
+      <c r="AJ335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A336">
+        <v>6021</v>
+      </c>
+      <c r="B336" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C336" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D336">
+        <v>80</v>
+      </c>
+      <c r="E336">
+        <v>100</v>
+      </c>
+      <c r="F336">
+        <v>100</v>
+      </c>
+      <c r="G336">
+        <v>100</v>
+      </c>
+      <c r="H336">
+        <v>100</v>
+      </c>
+      <c r="I336">
+        <v>100</v>
+      </c>
+      <c r="J336">
+        <v>100</v>
+      </c>
+      <c r="K336">
+        <v>100</v>
+      </c>
+      <c r="L336">
+        <v>100</v>
+      </c>
+      <c r="M336">
+        <v>10</v>
+      </c>
+      <c r="N336">
+        <v>2</v>
+      </c>
+      <c r="O336">
+        <v>100</v>
+      </c>
+      <c r="P336">
+        <v>100</v>
+      </c>
+      <c r="Q336">
+        <v>100</v>
+      </c>
+      <c r="R336">
+        <v>100</v>
+      </c>
+      <c r="S336">
+        <v>10</v>
+      </c>
+      <c r="T336">
+        <v>12</v>
+      </c>
+      <c r="U336" t="s">
+        <v>38</v>
+      </c>
+      <c r="V336" t="s">
+        <v>229</v>
+      </c>
+      <c r="W336" t="s">
+        <v>864</v>
+      </c>
+      <c r="X336">
+        <v>432</v>
+      </c>
+      <c r="Y336">
+        <v>360</v>
+      </c>
+      <c r="Z336">
+        <v>420</v>
+      </c>
+      <c r="AA336">
+        <v>160</v>
+      </c>
+      <c r="AB336" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC336" t="s">
+        <v>1227</v>
+      </c>
+      <c r="AD336" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AF336">
+        <v>240</v>
+      </c>
+      <c r="AG336" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AH336">
+        <v>0</v>
+      </c>
+      <c r="AI336">
+        <v>0.5</v>
+      </c>
+      <c r="AJ336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A337">
+        <v>6022</v>
+      </c>
+      <c r="B337" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C337" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D337">
+        <v>62</v>
+      </c>
+      <c r="E337">
+        <v>60</v>
+      </c>
+      <c r="F337">
+        <v>100</v>
+      </c>
+      <c r="G337">
+        <v>10</v>
+      </c>
+      <c r="H337">
+        <v>30</v>
+      </c>
+      <c r="I337">
+        <v>130</v>
+      </c>
+      <c r="J337">
+        <v>100</v>
+      </c>
+      <c r="K337">
+        <v>100</v>
+      </c>
+      <c r="L337">
+        <v>80</v>
+      </c>
+      <c r="M337">
+        <v>15</v>
+      </c>
+      <c r="N337">
+        <v>9</v>
+      </c>
+      <c r="O337">
+        <v>120</v>
+      </c>
+      <c r="P337">
+        <v>30</v>
+      </c>
+      <c r="Q337">
+        <v>90</v>
+      </c>
+      <c r="R337">
+        <v>90</v>
+      </c>
+      <c r="S337">
+        <v>10</v>
+      </c>
+      <c r="T337">
+        <v>12</v>
+      </c>
+      <c r="U337" t="s">
+        <v>38</v>
+      </c>
+      <c r="V337" t="s">
+        <v>160</v>
+      </c>
+      <c r="W337" t="s">
+        <v>532</v>
+      </c>
+      <c r="X337">
+        <v>1000</v>
+      </c>
+      <c r="Y337">
+        <v>750</v>
+      </c>
+      <c r="Z337">
+        <v>1000</v>
+      </c>
+      <c r="AA337">
+        <v>160</v>
+      </c>
+      <c r="AB337" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC337" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AD337" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF337">
+        <v>972</v>
+      </c>
+      <c r="AG337" t="s">
+        <v>1237</v>
+      </c>
+      <c r="AH337">
+        <v>0</v>
+      </c>
+      <c r="AI337">
+        <v>0.5</v>
+      </c>
+      <c r="AJ337">
         <v>1</v>
       </c>
     </row>
@@ -39484,7 +40778,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="G1" s="12" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
@@ -39510,52 +40804,52 @@
         <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>1034</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>1037</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>1039</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>1041</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>1042</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>1043</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>1044</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>1045</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>1046</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>1047</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>1048</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.4">
@@ -39563,19 +40857,19 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>1050</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>1051</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1052</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -39622,7 +40916,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C4">
         <v>1.6</v>
@@ -39631,10 +40925,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F4" t="s">
         <v>1054</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1055</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -39681,7 +40975,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C5">
         <v>1.1499999999999999</v>
@@ -39690,10 +40984,10 @@
         <v>1.5</v>
       </c>
       <c r="E5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F5" t="s">
         <v>1057</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1058</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -39740,7 +41034,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C6">
         <v>1.1000000000000001</v>
@@ -39749,10 +41043,10 @@
         <v>1.8</v>
       </c>
       <c r="E6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F6" t="s">
         <v>1060</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1061</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -39799,7 +41093,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C7">
         <v>1.2</v>
@@ -39808,10 +41102,10 @@
         <v>1.6</v>
       </c>
       <c r="E7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F7" t="s">
         <v>1063</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1064</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -39858,7 +41152,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C8">
         <v>1.3</v>
@@ -39867,10 +41161,10 @@
         <v>1.3</v>
       </c>
       <c r="E8" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F8" t="s">
         <v>1066</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1067</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -39917,7 +41211,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C9">
         <v>1.4</v>
@@ -39926,10 +41220,10 @@
         <v>1.4</v>
       </c>
       <c r="E9" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F9" t="s">
         <v>1069</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1070</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -39976,19 +41270,19 @@
         <v>200</v>
       </c>
       <c r="B10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
         <v>1071</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>1072</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1073</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -40052,7 +41346,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -40060,7 +41354,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -40068,7 +41362,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -40076,7 +41370,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -40084,7 +41378,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -40092,7 +41386,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
@@ -40100,7 +41394,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -40108,7 +41402,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
@@ -40116,7 +41410,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -40124,7 +41418,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
@@ -40132,7 +41426,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
@@ -40140,7 +41434,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
@@ -40148,7 +41442,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
@@ -40156,7 +41450,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
   </sheetData>
@@ -40180,30 +41474,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B1" t="s">
         <v>28</v>
       </c>
       <c r="C1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1" t="s">
         <v>1075</v>
       </c>
-      <c r="D1" t="s">
-        <v>1076</v>
-      </c>
       <c r="E1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F1" t="s">
         <v>1035</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -40214,10 +41508,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -40226,18 +41520,18 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F3" t="s">
         <v>1077</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -40246,18 +41540,18 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F4" t="s">
         <v>1079</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -40268,10 +41562,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B6" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -40280,10 +41574,10 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F6" t="s">
         <v>1081</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1082</v>
       </c>
     </row>
   </sheetData>
@@ -40302,7 +41596,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -41523,7 +42817,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>4</v>
@@ -41532,13 +42826,13 @@
         <v>11</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>14</v>
@@ -42282,21 +43576,21 @@
         <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L1" t="s">
         <v>16</v>
       </c>
       <c r="M1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="N1" t="s">
         <v>1021</v>
-      </c>
-      <c r="N1" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -42340,7 +43634,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -42560,7 +43854,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -42604,7 +43898,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -42692,7 +43986,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -43176,7 +44470,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B22">
         <v>120</v>
@@ -43484,7 +44778,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B29">
         <v>2000</v>
@@ -43528,7 +44822,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B30">
         <v>4000</v>
@@ -43612,18 +44906,18 @@
         <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L1" t="s">
         <v>16</v>
       </c>
       <c r="M1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B2" s="2">
         <v>100</v>
@@ -44525,7 +45819,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -44566,7 +45860,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -45140,7 +46434,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B39" s="3">
         <v>104</v>
@@ -45181,7 +46475,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B40" s="3">
         <v>106</v>
@@ -45307,13 +46601,13 @@
         <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L1" t="s">
         <v>16</v>
       </c>
       <c r="M1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
@@ -45751,7 +47045,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -45760,13 +47054,13 @@
         <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H1" t="s">
         <v>14</v>
@@ -45775,34 +47069,34 @@
         <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L1" t="s">
         <v>1099</v>
       </c>
-      <c r="L1" t="s">
-        <v>1100</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="T1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="U1" t="s">
         <v>1168</v>
       </c>
-      <c r="U1" t="s">
-        <v>1169</v>
-      </c>
       <c r="W1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="X1" t="s">
         <v>1183</v>
       </c>
-      <c r="X1" t="s">
-        <v>1184</v>
-      </c>
       <c r="Z1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.4">
@@ -45878,7 +47172,7 @@
         <v>2.799942862973166</v>
       </c>
       <c r="AA2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.4">
@@ -53443,21 +54737,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B1" t="s">
         <v>1029</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1030</v>
       </c>
-      <c r="C1" t="s">
-        <v>1031</v>
-      </c>
       <c r="E1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B2">
         <v>0.05</v>
@@ -53592,7 +54886,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B11">
         <v>7.4999999999999997E-2</v>
@@ -53633,50 +54927,50 @@
         <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="M1" t="s">
         <v>3</v>
       </c>
       <c r="N1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="O1" t="s">
         <v>3</v>
       </c>
       <c r="P1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="Q1" t="s">
         <v>3</v>
       </c>
       <c r="R1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="V1" t="s">
         <v>3</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="Z1" s="10" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="AB1"/>
       <c r="AC1" t="s">
         <v>3</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="AF1" t="s">
         <v>3</v>
       </c>
       <c r="AG1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="AH1" t="s">
         <v>1200</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.4">
@@ -64463,16 +65757,16 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C1" t="s">
         <v>1233</v>
       </c>
-      <c r="B1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>1234</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
@@ -65816,13 +67110,13 @@
         <v>3</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>1196</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>1197</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">

--- a/Other/RoStatProcessing.xlsx
+++ b/Other/RoStatProcessing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProjectsSSD\RagnarokRebuildTcp\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1BC145-16DC-4AFC-B66F-F14CB919AEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19434F6-8650-4998-8E08-8F2300D5F2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5486" yWindow="1586" windowWidth="24034" windowHeight="14691" xr2:uid="{1C41742B-2950-4FF8-AA39-6557869B44EA}"/>
+    <workbookView xWindow="5631" yWindow="4149" windowWidth="26323" windowHeight="12642" xr2:uid="{1C41742B-2950-4FF8-AA39-6557869B44EA}"/>
   </bookViews>
   <sheets>
     <sheet name="StatDef" sheetId="3" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3452" uniqueCount="1278">
   <si>
     <t>Id</t>
   </si>
@@ -3881,6 +3881,12 @@
   </si>
   <si>
     <t>Gig</t>
+  </si>
+  <si>
+    <t>DoddlerCustomMobs</t>
+  </si>
+  <si>
+    <t>Feature</t>
   </si>
 </sst>
 </file>
@@ -3986,12 +3992,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5AE4419D-5DB5-4D1B-9713-9E17C7E1903B}" name="Table1" displayName="Table1" ref="A1:AK425" totalsRowShown="0">
-  <autoFilter ref="A1:AK425" xr:uid="{5AE4419D-5DB5-4D1B-9713-9E17C7E1903B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5AE4419D-5DB5-4D1B-9713-9E17C7E1903B}" name="Table1" displayName="Table1" ref="A1:AL425" totalsRowShown="0">
+  <autoFilter ref="A1:AL425" xr:uid="{5AE4419D-5DB5-4D1B-9713-9E17C7E1903B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AK331">
     <sortCondition ref="A1:A425"/>
   </sortState>
-  <tableColumns count="37">
+  <tableColumns count="38">
     <tableColumn id="1" xr3:uid="{B859DFBF-EB68-4198-9FF0-FEBC6A5D6D92}" name="Id"/>
     <tableColumn id="2" xr3:uid="{A79D65AB-A01E-4B86-B9DF-A89CDC4EC4AA}" name="Code"/>
     <tableColumn id="3" xr3:uid="{EE52CDA5-01D0-433C-8F91-38DC3D87119D}" name="Name"/>
@@ -4029,6 +4035,7 @@
     <tableColumn id="34" xr3:uid="{C2F7284A-9A1E-41FB-B9B4-55E9E8237CF0}" name="ClientShadow"/>
     <tableColumn id="35" xr3:uid="{4A5E8A7E-1FED-40FB-B528-9E07702DC74A}" name="ClientSize"/>
     <tableColumn id="36" xr3:uid="{A1CBDEC4-7472-419D-A040-958DE222AA8B}" name="Flags"/>
+    <tableColumn id="38" xr3:uid="{6BCAD2AE-AAFA-4CFC-AC03-A9C328911CC9}" name="Feature"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4331,7 +4338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811A97A5-94A7-4FFA-A162-65D076B52481}">
-  <dimension ref="A1:AK337"/>
+  <dimension ref="A1:AL337"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.07421875" bestFit="1" customWidth="1"/>
@@ -4368,9 +4375,10 @@
     <col min="35" max="35" width="14.84375" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="11.3828125" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="36.3046875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="21.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4482,8 +4490,11 @@
       <c r="AK1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL1" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>3999</v>
       </c>
@@ -4590,7 +4601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>4000</v>
       </c>
@@ -4697,7 +4708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>4001</v>
       </c>
@@ -4804,7 +4815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4002</v>
       </c>
@@ -4911,7 +4922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4003</v>
       </c>
@@ -5018,7 +5029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>4004</v>
       </c>
@@ -5128,7 +5139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>4005</v>
       </c>
@@ -5235,7 +5246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>4006</v>
       </c>
@@ -5342,7 +5353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>4007</v>
       </c>
@@ -5449,7 +5460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>4008</v>
       </c>
@@ -5556,7 +5567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>4009</v>
       </c>
@@ -5666,7 +5677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>4010</v>
       </c>
@@ -5773,7 +5784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>4011</v>
       </c>
@@ -5883,7 +5894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>4012</v>
       </c>
@@ -5990,7 +6001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>4013</v>
       </c>
@@ -37180,7 +37191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A305">
         <v>4302</v>
       </c>
@@ -37287,7 +37298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A306">
         <v>4303</v>
       </c>
@@ -37394,7 +37405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A307">
         <v>4304</v>
       </c>
@@ -37501,7 +37512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A308">
         <v>4305</v>
       </c>
@@ -37608,7 +37619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A309">
         <v>4306</v>
       </c>
@@ -37718,7 +37729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A310">
         <v>4307</v>
       </c>
@@ -37828,7 +37839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A311">
         <v>4308</v>
       </c>
@@ -37935,7 +37946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A312">
         <v>4309</v>
       </c>
@@ -38042,7 +38053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A313">
         <v>4310</v>
       </c>
@@ -38149,7 +38160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A314">
         <v>4311</v>
       </c>
@@ -38256,7 +38267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A315">
         <v>4312</v>
       </c>
@@ -38363,7 +38374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A316">
         <v>5000</v>
       </c>
@@ -38470,7 +38481,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A317">
         <v>6000</v>
       </c>
@@ -38580,7 +38591,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="318" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A318">
         <v>6001</v>
       </c>
@@ -38687,7 +38698,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="319" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A319">
         <v>6002</v>
       </c>
@@ -38797,7 +38808,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="320" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A320">
         <v>6003</v>
       </c>
@@ -38906,8 +38917,11 @@
       <c r="AJ320">
         <v>1</v>
       </c>
-    </row>
-    <row r="321" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL320" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="321" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A321">
         <v>6004</v>
       </c>
@@ -39013,8 +39027,11 @@
       <c r="AJ321">
         <v>1</v>
       </c>
-    </row>
-    <row r="322" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL321" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="322" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A322">
         <v>6005</v>
       </c>
@@ -39123,8 +39140,11 @@
       <c r="AK322" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="323" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL322" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="323" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A323">
         <v>6006</v>
       </c>
@@ -39233,8 +39253,11 @@
       <c r="AJ323">
         <v>1</v>
       </c>
-    </row>
-    <row r="324" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL323" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="324" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A324">
         <v>6007</v>
       </c>
@@ -39343,8 +39366,11 @@
       <c r="AJ324">
         <v>1</v>
       </c>
-    </row>
-    <row r="325" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL324" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="325" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A325">
         <v>6008</v>
       </c>
@@ -39453,8 +39479,11 @@
       <c r="AJ325">
         <v>1</v>
       </c>
-    </row>
-    <row r="326" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL325" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="326" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A326">
         <v>6009</v>
       </c>
@@ -39563,8 +39592,11 @@
       <c r="AJ326">
         <v>1</v>
       </c>
-    </row>
-    <row r="327" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL326" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="327" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A327">
         <v>6010</v>
       </c>
@@ -39673,8 +39705,11 @@
       <c r="AJ327">
         <v>1</v>
       </c>
-    </row>
-    <row r="328" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL327" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="328" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A328">
         <v>6011</v>
       </c>
@@ -39783,8 +39818,11 @@
       <c r="AJ328">
         <v>1</v>
       </c>
-    </row>
-    <row r="329" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL328" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="329" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A329">
         <v>6012</v>
       </c>
@@ -39893,8 +39931,11 @@
       <c r="AJ329">
         <v>1.05</v>
       </c>
-    </row>
-    <row r="330" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL329" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="330" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A330">
         <v>6013</v>
       </c>
@@ -40003,8 +40044,11 @@
       <c r="AJ330">
         <v>1</v>
       </c>
-    </row>
-    <row r="331" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL330" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="331" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A331">
         <v>6014</v>
       </c>
@@ -40113,8 +40157,11 @@
       <c r="AJ331">
         <v>1</v>
       </c>
-    </row>
-    <row r="332" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="AL331" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="332" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A332">
         <v>6015</v>
       </c>
@@ -40221,7 +40268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A333">
         <v>6018</v>
       </c>
@@ -40328,7 +40375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A334">
         <v>6019</v>
       </c>
@@ -40435,7 +40482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A335">
         <v>6020</v>
       </c>
@@ -40542,7 +40589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A336">
         <v>6021</v>
       </c>
@@ -40649,7 +40696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A337">
         <v>6022</v>
       </c>
@@ -40754,6 +40801,9 @@
       </c>
       <c r="AJ337">
         <v>1</v>
+      </c>
+      <c r="AL337" t="s">
+        <v>1276</v>
       </c>
     </row>
   </sheetData>
